--- a/Test_Cases.xlsx
+++ b/Test_Cases.xlsx
@@ -1,30 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
+  <fileVersion appName="Calc"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView windowHeight="20360"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="DoRobot" sheetId="1" r:id="rId1"/>
-    <sheet name="Remote" sheetId="2" r:id="rId2"/>
-    <sheet name="PICO4" sheetId="3" r:id="rId3"/>
-    <sheet name="DataCollection" sheetId="4" r:id="rId4"/>
-    <sheet name="Sheet4" sheetId="5" r:id="rId5"/>
+    <sheet name="DoRobot" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="Remote" sheetId="2" state="visible" r:id="rId3"/>
+    <sheet name="PICO4" sheetId="3" state="visible" r:id="rId4"/>
+    <sheet name="DataCollection" sheetId="4" state="visible" r:id="rId5"/>
+    <sheet name="Sheet4" sheetId="5" state="visible" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
   </extLst>
 </workbook>
@@ -33,344 +26,206 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="51">
   <si>
-    <t>ID</t>
+    <t xml:space="preserve">ID</t>
   </si>
   <si>
     <t xml:space="preserve">Component </t>
   </si>
   <si>
-    <t>Version</t>
-  </si>
-  <si>
-    <t>Category</t>
-  </si>
-  <si>
-    <t>Test case</t>
-  </si>
-  <si>
-    <t>Issue Description</t>
+    <t xml:space="preserve">Version</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test case</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Issue Description</t>
   </si>
   <si>
     <t xml:space="preserve">Severity </t>
   </si>
   <si>
-    <t>Fix</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Q1001</t>
-  </si>
-  <si>
-    <t>DoRobot</t>
-  </si>
-  <si>
-    <t>1.0.200</t>
-  </si>
-  <si>
-    <t>Device connectivity &amp; stability</t>
+    <t xml:space="preserve">Fix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q1001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DoRobot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0.200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Device connectivity &amp; stability</t>
   </si>
   <si>
     <t xml:space="preserve">Sensor disconnect after 45min continuous run </t>
   </si>
   <si>
-    <t>Critical</t>
-  </si>
-  <si>
-    <t>FAIL</t>
-  </si>
-  <si>
-    <t>Q1002</t>
-  </si>
-  <si>
-    <t>0.1.0</t>
-  </si>
-  <si>
-    <t>Q1003</t>
-  </si>
-  <si>
-    <t>Runtime robustness (restart/recovery)</t>
-  </si>
-  <si>
-    <t>Q1004</t>
-  </si>
-  <si>
-    <t>Q1005</t>
-  </si>
-  <si>
-    <t>Live telemetry visualization</t>
-  </si>
-  <si>
-    <t>Q1006</t>
-  </si>
-  <si>
-    <t>Q1007</t>
-  </si>
-  <si>
-    <t>Playback &amp; log review usability</t>
-  </si>
-  <si>
-    <t>Q1008</t>
-  </si>
-  <si>
-    <t>PASS with workaround</t>
-  </si>
-  <si>
-    <t>Q1009</t>
-  </si>
-  <si>
-    <t>Performance observations</t>
-  </si>
-  <si>
-    <t>Encoding takes too long time</t>
-  </si>
-  <si>
-    <t>Minor</t>
+    <t xml:space="preserve">Critical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAIL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q1002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q1003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Runtime robustness (restart/recovery)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q1004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q1005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Live telemetry visualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q1006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q1007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Playback &amp; log review usability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q1008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PASS with workaround</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q1009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Performance observations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Encoding takes too long time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minor</t>
   </si>
   <si>
     <t xml:space="preserve">FW update v2.3 </t>
   </si>
   <si>
-    <t>PASS</t>
-  </si>
-  <si>
-    <t>Q1010</t>
-  </si>
-  <si>
-    <t>推理限位问题</t>
-  </si>
-  <si>
-    <t>DEFERRED</t>
-  </si>
-  <si>
-    <t>Q2001</t>
-  </si>
-  <si>
-    <t>Remote controller</t>
-  </si>
-  <si>
-    <t>Q2002</t>
-  </si>
-  <si>
-    <t>Q3001</t>
-  </si>
-  <si>
-    <t>PICO VR</t>
-  </si>
-  <si>
-    <t>Q3002</t>
-  </si>
-  <si>
-    <t>Q4001</t>
-  </si>
-  <si>
-    <t>Annotation</t>
-  </si>
-  <si>
-    <t>No tag defined</t>
-  </si>
-  <si>
-    <t>Q4002</t>
-  </si>
-  <si>
-    <t>data upload</t>
-  </si>
-  <si>
-    <t>upload exception</t>
-  </si>
-  <si>
-    <t>Q4003</t>
-  </si>
-  <si>
-    <t>Q4004</t>
+    <t xml:space="preserve">PASS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q1010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">推理限位问题</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DEFERRED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q2001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remote controller</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q2002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q3001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PICO VR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q3002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q4001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annotation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No tag defined</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q4002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data upload</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upload exception</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q4003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q4004</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="6">
     <font>
       <sz val="12"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <family val="0"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="12"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <family val="0"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF333333"/>
       <name val="Arial"/>
+      <family val="0"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="34">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -380,875 +235,150 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+        <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
-    <border>
+  <borders count="2">
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
   <cellXfs count="9">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="0E2841"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="156082"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="E97132"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="196B24"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="A02B93"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="4EA72E"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="467886"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="96607D"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Aptos Display"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Aptos Narrow"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
-</a:theme>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:I36"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="17.6"/>
+  <sheetFormatPr defaultColWidth="11.0234375" defaultRowHeight="17.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="8.5625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="15.625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="13.1875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="21.7638888888889" style="3" customWidth="1"/>
-    <col min="5" max="5" width="31.4722222222222" style="3" customWidth="1"/>
-    <col min="6" max="6" width="25.4652777777778" style="2" customWidth="1"/>
-    <col min="7" max="7" width="11" style="2"/>
-    <col min="8" max="8" width="15.3888888888889" style="3" customWidth="1"/>
-    <col min="9" max="9" width="19.3263888888889" style="3" customWidth="1"/>
-    <col min="10" max="16384" width="11" style="2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="15.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="13.19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="21.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="31.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="25.47"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="15.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="19.33"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="10" style="1" width="11"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="31" customHeight="1" spans="1:9">
-      <c r="A1" s="4" t="s">
+    <row r="1" s="5" customFormat="true" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" s="2" customFormat="1" ht="35" customHeight="1" spans="1:9">
+    <row r="2" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
@@ -1268,12 +398,14 @@
       <c r="G2" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="7"/>
+      <c r="H2" s="7" t="n">
+        <v>1</v>
+      </c>
       <c r="I2" s="7" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="1" ht="40" customHeight="1" spans="1:9">
+    <row r="3" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
         <v>16</v>
       </c>
@@ -1292,7 +424,7 @@
       <c r="H3" s="7"/>
       <c r="I3" s="7"/>
     </row>
-    <row r="4" s="2" customFormat="1" ht="40" customHeight="1" spans="1:9">
+    <row r="4" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
         <v>18</v>
       </c>
@@ -1309,7 +441,7 @@
       <c r="H4" s="7"/>
       <c r="I4" s="7"/>
     </row>
-    <row r="5" s="2" customFormat="1" ht="38" customHeight="1" spans="1:9">
+    <row r="5" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
         <v>20</v>
       </c>
@@ -1326,7 +458,7 @@
       <c r="H5" s="7"/>
       <c r="I5" s="7"/>
     </row>
-    <row r="6" s="2" customFormat="1" ht="38" customHeight="1" spans="1:9">
+    <row r="6" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
         <v>21</v>
       </c>
@@ -1343,7 +475,7 @@
       <c r="H6" s="7"/>
       <c r="I6" s="7"/>
     </row>
-    <row r="7" s="2" customFormat="1" ht="38" customHeight="1" spans="1:9">
+    <row r="7" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
         <v>23</v>
       </c>
@@ -1360,7 +492,7 @@
       <c r="H7" s="7"/>
       <c r="I7" s="7"/>
     </row>
-    <row r="8" s="2" customFormat="1" ht="44" customHeight="1" spans="1:9">
+    <row r="8" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
         <v>24</v>
       </c>
@@ -1377,7 +509,7 @@
       <c r="H8" s="7"/>
       <c r="I8" s="7"/>
     </row>
-    <row r="9" s="2" customFormat="1" ht="62" customHeight="1" spans="1:9">
+    <row r="9" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
         <v>26</v>
       </c>
@@ -1396,7 +528,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" s="2" customFormat="1" ht="62" customHeight="1" spans="1:9">
+    <row r="10" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
         <v>28</v>
       </c>
@@ -1421,7 +553,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" s="2" customFormat="1" ht="58" customHeight="1" spans="1:9">
+    <row r="11" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
         <v>34</v>
       </c>
@@ -1444,7 +576,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="12" s="2" customFormat="1" spans="1:9">
+    <row r="12" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6"/>
       <c r="B12" s="7"/>
       <c r="C12" s="6"/>
@@ -1455,7 +587,7 @@
       <c r="H12" s="7"/>
       <c r="I12" s="7"/>
     </row>
-    <row r="13" s="2" customFormat="1" spans="1:9">
+    <row r="13" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6"/>
       <c r="B13" s="7"/>
       <c r="C13" s="6"/>
@@ -1466,7 +598,7 @@
       <c r="H13" s="7"/>
       <c r="I13" s="7"/>
     </row>
-    <row r="14" s="2" customFormat="1" spans="1:9">
+    <row r="14" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6"/>
       <c r="B14" s="7"/>
       <c r="C14" s="6"/>
@@ -1477,7 +609,7 @@
       <c r="H14" s="7"/>
       <c r="I14" s="7"/>
     </row>
-    <row r="15" s="2" customFormat="1" spans="1:9">
+    <row r="15" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6"/>
       <c r="B15" s="7"/>
       <c r="C15" s="6"/>
@@ -1488,7 +620,7 @@
       <c r="H15" s="7"/>
       <c r="I15" s="7"/>
     </row>
-    <row r="16" s="2" customFormat="1" spans="1:9">
+    <row r="16" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6"/>
       <c r="B16" s="7"/>
       <c r="C16" s="6"/>
@@ -1499,7 +631,7 @@
       <c r="H16" s="7"/>
       <c r="I16" s="7"/>
     </row>
-    <row r="17" s="2" customFormat="1" spans="1:9">
+    <row r="17" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6"/>
       <c r="B17" s="7"/>
       <c r="C17" s="6"/>
@@ -1510,7 +642,7 @@
       <c r="H17" s="7"/>
       <c r="I17" s="7"/>
     </row>
-    <row r="18" s="2" customFormat="1" spans="1:9">
+    <row r="18" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6"/>
       <c r="B18" s="7"/>
       <c r="C18" s="6"/>
@@ -1521,7 +653,7 @@
       <c r="H18" s="7"/>
       <c r="I18" s="7"/>
     </row>
-    <row r="19" s="2" customFormat="1" spans="1:9">
+    <row r="19" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6"/>
       <c r="B19" s="7"/>
       <c r="C19" s="6"/>
@@ -1532,7 +664,7 @@
       <c r="H19" s="7"/>
       <c r="I19" s="7"/>
     </row>
-    <row r="20" s="2" customFormat="1" spans="1:9">
+    <row r="20" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6"/>
       <c r="B20" s="7"/>
       <c r="C20" s="6"/>
@@ -1543,7 +675,7 @@
       <c r="H20" s="7"/>
       <c r="I20" s="7"/>
     </row>
-    <row r="21" s="2" customFormat="1" spans="1:9">
+    <row r="21" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6"/>
       <c r="B21" s="7"/>
       <c r="C21" s="6"/>
@@ -1554,7 +686,7 @@
       <c r="H21" s="7"/>
       <c r="I21" s="7"/>
     </row>
-    <row r="22" s="2" customFormat="1" spans="1:9">
+    <row r="22" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6"/>
       <c r="B22" s="7"/>
       <c r="C22" s="6"/>
@@ -1565,7 +697,7 @@
       <c r="H22" s="7"/>
       <c r="I22" s="7"/>
     </row>
-    <row r="23" s="2" customFormat="1" spans="1:9">
+    <row r="23" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6"/>
       <c r="B23" s="7"/>
       <c r="C23" s="6"/>
@@ -1576,7 +708,7 @@
       <c r="H23" s="7"/>
       <c r="I23" s="7"/>
     </row>
-    <row r="24" s="2" customFormat="1" spans="1:9">
+    <row r="24" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6"/>
       <c r="B24" s="7"/>
       <c r="C24" s="6"/>
@@ -1587,7 +719,7 @@
       <c r="H24" s="7"/>
       <c r="I24" s="7"/>
     </row>
-    <row r="25" s="2" customFormat="1" spans="1:9">
+    <row r="25" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6"/>
       <c r="B25" s="7"/>
       <c r="C25" s="6"/>
@@ -1598,7 +730,7 @@
       <c r="H25" s="7"/>
       <c r="I25" s="7"/>
     </row>
-    <row r="26" s="2" customFormat="1" spans="1:9">
+    <row r="26" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6"/>
       <c r="B26" s="7"/>
       <c r="C26" s="6"/>
@@ -1609,7 +741,7 @@
       <c r="H26" s="7"/>
       <c r="I26" s="7"/>
     </row>
-    <row r="27" s="2" customFormat="1" spans="1:9">
+    <row r="27" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6"/>
       <c r="B27" s="7"/>
       <c r="C27" s="6"/>
@@ -1620,7 +752,7 @@
       <c r="H27" s="7"/>
       <c r="I27" s="7"/>
     </row>
-    <row r="28" s="2" customFormat="1" spans="1:9">
+    <row r="28" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6"/>
       <c r="B28" s="7"/>
       <c r="C28" s="6"/>
@@ -1631,7 +763,7 @@
       <c r="H28" s="7"/>
       <c r="I28" s="7"/>
     </row>
-    <row r="29" s="2" customFormat="1" spans="1:9">
+    <row r="29" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6"/>
       <c r="B29" s="7"/>
       <c r="C29" s="6"/>
@@ -1642,7 +774,7 @@
       <c r="H29" s="7"/>
       <c r="I29" s="7"/>
     </row>
-    <row r="30" s="2" customFormat="1" spans="1:9">
+    <row r="30" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6"/>
       <c r="B30" s="7"/>
       <c r="C30" s="6"/>
@@ -1653,7 +785,7 @@
       <c r="H30" s="7"/>
       <c r="I30" s="7"/>
     </row>
-    <row r="31" s="2" customFormat="1" spans="1:9">
+    <row r="31" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="6"/>
       <c r="B31" s="7"/>
       <c r="C31" s="6"/>
@@ -1664,7 +796,7 @@
       <c r="H31" s="7"/>
       <c r="I31" s="7"/>
     </row>
-    <row r="32" s="2" customFormat="1" spans="1:9">
+    <row r="32" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="6"/>
       <c r="B32" s="7"/>
       <c r="C32" s="6"/>
@@ -1675,7 +807,7 @@
       <c r="H32" s="7"/>
       <c r="I32" s="7"/>
     </row>
-    <row r="33" s="2" customFormat="1" spans="1:9">
+    <row r="33" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="6"/>
       <c r="B33" s="7"/>
       <c r="C33" s="6"/>
@@ -1686,7 +818,7 @@
       <c r="H33" s="7"/>
       <c r="I33" s="7"/>
     </row>
-    <row r="34" s="2" customFormat="1" spans="1:9">
+    <row r="34" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6"/>
       <c r="B34" s="7"/>
       <c r="C34" s="6"/>
@@ -1697,7 +829,7 @@
       <c r="H34" s="7"/>
       <c r="I34" s="7"/>
     </row>
-    <row r="35" s="2" customFormat="1" spans="1:9">
+    <row r="35" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="6"/>
       <c r="B35" s="7"/>
       <c r="C35" s="6"/>
@@ -1708,7 +840,7 @@
       <c r="H35" s="7"/>
       <c r="I35" s="7"/>
     </row>
-    <row r="36" s="2" customFormat="1" spans="1:9">
+    <row r="36" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="6"/>
       <c r="B36" s="7"/>
       <c r="C36" s="6"/>
@@ -1720,59 +852,66 @@
       <c r="I36" s="7"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:I35"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="17.6"/>
+  <sheetFormatPr defaultColWidth="11.0234375" defaultRowHeight="17.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="8.5625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="15.625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="13.1875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="21.7638888888889" style="3" customWidth="1"/>
-    <col min="5" max="5" width="31.4722222222222" style="3" customWidth="1"/>
-    <col min="6" max="6" width="25.4652777777778" style="2" customWidth="1"/>
-    <col min="7" max="7" width="11" style="2"/>
-    <col min="8" max="8" width="15.3888888888889" style="3" customWidth="1"/>
-    <col min="9" max="9" width="19.3263888888889" style="3" customWidth="1"/>
-    <col min="10" max="16384" width="11" style="2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="15.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="13.19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="21.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="31.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="25.47"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="15.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="19.33"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="10" style="1" width="11"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="31" customHeight="1" spans="1:9">
-      <c r="A1" s="4" t="s">
+    <row r="1" s="5" customFormat="true" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" s="2" customFormat="1" ht="40" customHeight="1" spans="1:9">
+    <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
         <v>37</v>
       </c>
@@ -1791,7 +930,7 @@
       <c r="H2" s="7"/>
       <c r="I2" s="7"/>
     </row>
-    <row r="3" s="2" customFormat="1" ht="40" customHeight="1" spans="1:9">
+    <row r="3" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
         <v>39</v>
       </c>
@@ -1808,7 +947,7 @@
       <c r="H3" s="7"/>
       <c r="I3" s="7"/>
     </row>
-    <row r="4" s="2" customFormat="1" ht="38" customHeight="1" spans="1:9">
+    <row r="4" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
         <v>20</v>
       </c>
@@ -1825,7 +964,7 @@
       <c r="H4" s="7"/>
       <c r="I4" s="7"/>
     </row>
-    <row r="5" s="2" customFormat="1" ht="38" customHeight="1" spans="1:9">
+    <row r="5" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6"/>
       <c r="B5" s="7" t="s">
         <v>38</v>
@@ -1840,7 +979,7 @@
       <c r="H5" s="7"/>
       <c r="I5" s="7"/>
     </row>
-    <row r="6" s="2" customFormat="1" ht="38" customHeight="1" spans="1:9">
+    <row r="6" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="7" t="s">
         <v>38</v>
@@ -1855,7 +994,7 @@
       <c r="H6" s="7"/>
       <c r="I6" s="7"/>
     </row>
-    <row r="7" s="2" customFormat="1" ht="44" customHeight="1" spans="1:9">
+    <row r="7" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6"/>
       <c r="B7" s="7" t="s">
         <v>38</v>
@@ -1870,7 +1009,7 @@
       <c r="H7" s="7"/>
       <c r="I7" s="7"/>
     </row>
-    <row r="8" s="2" customFormat="1" ht="62" customHeight="1" spans="1:9">
+    <row r="8" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6"/>
       <c r="B8" s="7" t="s">
         <v>38</v>
@@ -1887,7 +1026,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" s="2" customFormat="1" ht="62" customHeight="1" spans="1:9">
+    <row r="9" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6"/>
       <c r="B9" s="7" t="s">
         <v>38</v>
@@ -1910,7 +1049,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" s="2" customFormat="1" ht="58" customHeight="1" spans="1:9">
+    <row r="10" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6"/>
       <c r="B10" s="7"/>
       <c r="C10" s="6"/>
@@ -1921,7 +1060,7 @@
       <c r="H10" s="7"/>
       <c r="I10" s="7"/>
     </row>
-    <row r="11" s="2" customFormat="1" spans="1:9">
+    <row r="11" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6"/>
       <c r="B11" s="7"/>
       <c r="C11" s="6"/>
@@ -1932,7 +1071,7 @@
       <c r="H11" s="7"/>
       <c r="I11" s="7"/>
     </row>
-    <row r="12" s="2" customFormat="1" spans="1:9">
+    <row r="12" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6"/>
       <c r="B12" s="7"/>
       <c r="C12" s="6"/>
@@ -1943,7 +1082,7 @@
       <c r="H12" s="7"/>
       <c r="I12" s="7"/>
     </row>
-    <row r="13" s="2" customFormat="1" spans="1:9">
+    <row r="13" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6"/>
       <c r="B13" s="7"/>
       <c r="C13" s="6"/>
@@ -1954,7 +1093,7 @@
       <c r="H13" s="7"/>
       <c r="I13" s="7"/>
     </row>
-    <row r="14" s="2" customFormat="1" spans="1:9">
+    <row r="14" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6"/>
       <c r="B14" s="7"/>
       <c r="C14" s="6"/>
@@ -1965,7 +1104,7 @@
       <c r="H14" s="7"/>
       <c r="I14" s="7"/>
     </row>
-    <row r="15" s="2" customFormat="1" spans="1:9">
+    <row r="15" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6"/>
       <c r="B15" s="7"/>
       <c r="C15" s="6"/>
@@ -1976,7 +1115,7 @@
       <c r="H15" s="7"/>
       <c r="I15" s="7"/>
     </row>
-    <row r="16" s="2" customFormat="1" spans="1:9">
+    <row r="16" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6"/>
       <c r="B16" s="7"/>
       <c r="C16" s="6"/>
@@ -1987,7 +1126,7 @@
       <c r="H16" s="7"/>
       <c r="I16" s="7"/>
     </row>
-    <row r="17" s="2" customFormat="1" spans="1:9">
+    <row r="17" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6"/>
       <c r="B17" s="7"/>
       <c r="C17" s="6"/>
@@ -1998,7 +1137,7 @@
       <c r="H17" s="7"/>
       <c r="I17" s="7"/>
     </row>
-    <row r="18" s="2" customFormat="1" spans="1:9">
+    <row r="18" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6"/>
       <c r="B18" s="7"/>
       <c r="C18" s="6"/>
@@ -2009,7 +1148,7 @@
       <c r="H18" s="7"/>
       <c r="I18" s="7"/>
     </row>
-    <row r="19" s="2" customFormat="1" spans="1:9">
+    <row r="19" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6"/>
       <c r="B19" s="7"/>
       <c r="C19" s="6"/>
@@ -2020,7 +1159,7 @@
       <c r="H19" s="7"/>
       <c r="I19" s="7"/>
     </row>
-    <row r="20" s="2" customFormat="1" spans="1:9">
+    <row r="20" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6"/>
       <c r="B20" s="7"/>
       <c r="C20" s="6"/>
@@ -2031,7 +1170,7 @@
       <c r="H20" s="7"/>
       <c r="I20" s="7"/>
     </row>
-    <row r="21" s="2" customFormat="1" spans="1:9">
+    <row r="21" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6"/>
       <c r="B21" s="7"/>
       <c r="C21" s="6"/>
@@ -2042,7 +1181,7 @@
       <c r="H21" s="7"/>
       <c r="I21" s="7"/>
     </row>
-    <row r="22" s="2" customFormat="1" spans="1:9">
+    <row r="22" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6"/>
       <c r="B22" s="7"/>
       <c r="C22" s="6"/>
@@ -2053,7 +1192,7 @@
       <c r="H22" s="7"/>
       <c r="I22" s="7"/>
     </row>
-    <row r="23" s="2" customFormat="1" spans="1:9">
+    <row r="23" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6"/>
       <c r="B23" s="7"/>
       <c r="C23" s="6"/>
@@ -2064,7 +1203,7 @@
       <c r="H23" s="7"/>
       <c r="I23" s="7"/>
     </row>
-    <row r="24" s="2" customFormat="1" spans="1:9">
+    <row r="24" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6"/>
       <c r="B24" s="7"/>
       <c r="C24" s="6"/>
@@ -2075,7 +1214,7 @@
       <c r="H24" s="7"/>
       <c r="I24" s="7"/>
     </row>
-    <row r="25" s="2" customFormat="1" spans="1:9">
+    <row r="25" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6"/>
       <c r="B25" s="7"/>
       <c r="C25" s="6"/>
@@ -2086,7 +1225,7 @@
       <c r="H25" s="7"/>
       <c r="I25" s="7"/>
     </row>
-    <row r="26" s="2" customFormat="1" spans="1:9">
+    <row r="26" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6"/>
       <c r="B26" s="7"/>
       <c r="C26" s="6"/>
@@ -2097,7 +1236,7 @@
       <c r="H26" s="7"/>
       <c r="I26" s="7"/>
     </row>
-    <row r="27" s="2" customFormat="1" spans="1:9">
+    <row r="27" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6"/>
       <c r="B27" s="7"/>
       <c r="C27" s="6"/>
@@ -2108,7 +1247,7 @@
       <c r="H27" s="7"/>
       <c r="I27" s="7"/>
     </row>
-    <row r="28" s="2" customFormat="1" spans="1:9">
+    <row r="28" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6"/>
       <c r="B28" s="7"/>
       <c r="C28" s="6"/>
@@ -2119,7 +1258,7 @@
       <c r="H28" s="7"/>
       <c r="I28" s="7"/>
     </row>
-    <row r="29" s="2" customFormat="1" spans="1:9">
+    <row r="29" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6"/>
       <c r="B29" s="7"/>
       <c r="C29" s="6"/>
@@ -2130,7 +1269,7 @@
       <c r="H29" s="7"/>
       <c r="I29" s="7"/>
     </row>
-    <row r="30" s="2" customFormat="1" spans="1:9">
+    <row r="30" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6"/>
       <c r="B30" s="7"/>
       <c r="C30" s="6"/>
@@ -2141,7 +1280,7 @@
       <c r="H30" s="7"/>
       <c r="I30" s="7"/>
     </row>
-    <row r="31" s="2" customFormat="1" spans="1:9">
+    <row r="31" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="6"/>
       <c r="B31" s="7"/>
       <c r="C31" s="6"/>
@@ -2152,7 +1291,7 @@
       <c r="H31" s="7"/>
       <c r="I31" s="7"/>
     </row>
-    <row r="32" s="2" customFormat="1" spans="1:9">
+    <row r="32" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="6"/>
       <c r="B32" s="7"/>
       <c r="C32" s="6"/>
@@ -2163,7 +1302,7 @@
       <c r="H32" s="7"/>
       <c r="I32" s="7"/>
     </row>
-    <row r="33" s="2" customFormat="1" spans="1:9">
+    <row r="33" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="6"/>
       <c r="B33" s="7"/>
       <c r="C33" s="6"/>
@@ -2174,7 +1313,7 @@
       <c r="H33" s="7"/>
       <c r="I33" s="7"/>
     </row>
-    <row r="34" s="2" customFormat="1" spans="1:9">
+    <row r="34" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6"/>
       <c r="B34" s="7"/>
       <c r="C34" s="6"/>
@@ -2185,7 +1324,7 @@
       <c r="H34" s="7"/>
       <c r="I34" s="7"/>
     </row>
-    <row r="35" s="2" customFormat="1" spans="1:9">
+    <row r="35" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="6"/>
       <c r="B35" s="7"/>
       <c r="C35" s="6"/>
@@ -2197,59 +1336,66 @@
       <c r="I35" s="7"/>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:I36"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="17.6"/>
+  <sheetFormatPr defaultColWidth="11.0234375" defaultRowHeight="17.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="8.5625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="15.625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="13.1875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="21.7638888888889" style="3" customWidth="1"/>
-    <col min="5" max="5" width="31.4722222222222" style="3" customWidth="1"/>
-    <col min="6" max="6" width="25.4652777777778" style="2" customWidth="1"/>
-    <col min="7" max="7" width="11" style="2"/>
-    <col min="8" max="8" width="15.3888888888889" style="3" customWidth="1"/>
-    <col min="9" max="9" width="19.3263888888889" style="3" customWidth="1"/>
-    <col min="10" max="16384" width="11" style="2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="15.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="13.19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="21.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="31.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="25.47"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="15.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="19.33"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="10" style="1" width="11"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="31" customHeight="1" spans="1:9">
-      <c r="A1" s="4" t="s">
+    <row r="1" s="5" customFormat="true" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" s="2" customFormat="1" ht="35" customHeight="1" spans="1:9">
+    <row r="2" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
         <v>40</v>
       </c>
@@ -2274,7 +1420,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="1" ht="40" customHeight="1" spans="1:9">
+    <row r="3" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
         <v>42</v>
       </c>
@@ -2293,7 +1439,7 @@
       <c r="H3" s="7"/>
       <c r="I3" s="7"/>
     </row>
-    <row r="4" s="2" customFormat="1" ht="40" customHeight="1" spans="1:9">
+    <row r="4" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
         <v>18</v>
       </c>
@@ -2310,7 +1456,7 @@
       <c r="H4" s="7"/>
       <c r="I4" s="7"/>
     </row>
-    <row r="5" s="2" customFormat="1" ht="38" customHeight="1" spans="1:9">
+    <row r="5" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
         <v>20</v>
       </c>
@@ -2327,7 +1473,7 @@
       <c r="H5" s="7"/>
       <c r="I5" s="7"/>
     </row>
-    <row r="6" s="2" customFormat="1" ht="38" customHeight="1" spans="1:9">
+    <row r="6" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
         <v>21</v>
       </c>
@@ -2344,7 +1490,7 @@
       <c r="H6" s="7"/>
       <c r="I6" s="7"/>
     </row>
-    <row r="7" s="2" customFormat="1" ht="38" customHeight="1" spans="1:9">
+    <row r="7" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
         <v>23</v>
       </c>
@@ -2361,7 +1507,7 @@
       <c r="H7" s="7"/>
       <c r="I7" s="7"/>
     </row>
-    <row r="8" s="2" customFormat="1" ht="44" customHeight="1" spans="1:9">
+    <row r="8" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
         <v>24</v>
       </c>
@@ -2378,7 +1524,7 @@
       <c r="H8" s="7"/>
       <c r="I8" s="7"/>
     </row>
-    <row r="9" s="2" customFormat="1" ht="62" customHeight="1" spans="1:9">
+    <row r="9" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
         <v>26</v>
       </c>
@@ -2397,7 +1543,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" s="2" customFormat="1" ht="62" customHeight="1" spans="1:9">
+    <row r="10" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
         <v>28</v>
       </c>
@@ -2422,7 +1568,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" s="2" customFormat="1" ht="58" customHeight="1" spans="1:9">
+    <row r="11" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
         <v>34</v>
       </c>
@@ -2445,7 +1591,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="12" s="2" customFormat="1" spans="1:9">
+    <row r="12" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6"/>
       <c r="B12" s="7"/>
       <c r="C12" s="6"/>
@@ -2456,7 +1602,7 @@
       <c r="H12" s="7"/>
       <c r="I12" s="7"/>
     </row>
-    <row r="13" s="2" customFormat="1" spans="1:9">
+    <row r="13" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6"/>
       <c r="B13" s="7"/>
       <c r="C13" s="6"/>
@@ -2467,7 +1613,7 @@
       <c r="H13" s="7"/>
       <c r="I13" s="7"/>
     </row>
-    <row r="14" s="2" customFormat="1" spans="1:9">
+    <row r="14" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6"/>
       <c r="B14" s="7"/>
       <c r="C14" s="6"/>
@@ -2478,7 +1624,7 @@
       <c r="H14" s="7"/>
       <c r="I14" s="7"/>
     </row>
-    <row r="15" s="2" customFormat="1" spans="1:9">
+    <row r="15" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6"/>
       <c r="B15" s="7"/>
       <c r="C15" s="6"/>
@@ -2489,7 +1635,7 @@
       <c r="H15" s="7"/>
       <c r="I15" s="7"/>
     </row>
-    <row r="16" s="2" customFormat="1" spans="1:9">
+    <row r="16" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6"/>
       <c r="B16" s="7"/>
       <c r="C16" s="6"/>
@@ -2500,7 +1646,7 @@
       <c r="H16" s="7"/>
       <c r="I16" s="7"/>
     </row>
-    <row r="17" s="2" customFormat="1" spans="1:9">
+    <row r="17" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6"/>
       <c r="B17" s="7"/>
       <c r="C17" s="6"/>
@@ -2511,7 +1657,7 @@
       <c r="H17" s="7"/>
       <c r="I17" s="7"/>
     </row>
-    <row r="18" s="2" customFormat="1" spans="1:9">
+    <row r="18" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6"/>
       <c r="B18" s="7"/>
       <c r="C18" s="6"/>
@@ -2522,7 +1668,7 @@
       <c r="H18" s="7"/>
       <c r="I18" s="7"/>
     </row>
-    <row r="19" s="2" customFormat="1" spans="1:9">
+    <row r="19" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6"/>
       <c r="B19" s="7"/>
       <c r="C19" s="6"/>
@@ -2533,7 +1679,7 @@
       <c r="H19" s="7"/>
       <c r="I19" s="7"/>
     </row>
-    <row r="20" s="2" customFormat="1" spans="1:9">
+    <row r="20" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6"/>
       <c r="B20" s="7"/>
       <c r="C20" s="6"/>
@@ -2544,7 +1690,7 @@
       <c r="H20" s="7"/>
       <c r="I20" s="7"/>
     </row>
-    <row r="21" s="2" customFormat="1" spans="1:9">
+    <row r="21" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6"/>
       <c r="B21" s="7"/>
       <c r="C21" s="6"/>
@@ -2555,7 +1701,7 @@
       <c r="H21" s="7"/>
       <c r="I21" s="7"/>
     </row>
-    <row r="22" s="2" customFormat="1" spans="1:9">
+    <row r="22" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6"/>
       <c r="B22" s="7"/>
       <c r="C22" s="6"/>
@@ -2566,7 +1712,7 @@
       <c r="H22" s="7"/>
       <c r="I22" s="7"/>
     </row>
-    <row r="23" s="2" customFormat="1" spans="1:9">
+    <row r="23" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6"/>
       <c r="B23" s="7"/>
       <c r="C23" s="6"/>
@@ -2577,7 +1723,7 @@
       <c r="H23" s="7"/>
       <c r="I23" s="7"/>
     </row>
-    <row r="24" s="2" customFormat="1" spans="1:9">
+    <row r="24" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6"/>
       <c r="B24" s="7"/>
       <c r="C24" s="6"/>
@@ -2588,7 +1734,7 @@
       <c r="H24" s="7"/>
       <c r="I24" s="7"/>
     </row>
-    <row r="25" s="2" customFormat="1" spans="1:9">
+    <row r="25" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6"/>
       <c r="B25" s="7"/>
       <c r="C25" s="6"/>
@@ -2599,7 +1745,7 @@
       <c r="H25" s="7"/>
       <c r="I25" s="7"/>
     </row>
-    <row r="26" s="2" customFormat="1" spans="1:9">
+    <row r="26" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6"/>
       <c r="B26" s="7"/>
       <c r="C26" s="6"/>
@@ -2610,7 +1756,7 @@
       <c r="H26" s="7"/>
       <c r="I26" s="7"/>
     </row>
-    <row r="27" s="2" customFormat="1" spans="1:9">
+    <row r="27" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6"/>
       <c r="B27" s="7"/>
       <c r="C27" s="6"/>
@@ -2621,7 +1767,7 @@
       <c r="H27" s="7"/>
       <c r="I27" s="7"/>
     </row>
-    <row r="28" s="2" customFormat="1" spans="1:9">
+    <row r="28" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6"/>
       <c r="B28" s="7"/>
       <c r="C28" s="6"/>
@@ -2632,7 +1778,7 @@
       <c r="H28" s="7"/>
       <c r="I28" s="7"/>
     </row>
-    <row r="29" s="2" customFormat="1" spans="1:9">
+    <row r="29" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6"/>
       <c r="B29" s="7"/>
       <c r="C29" s="6"/>
@@ -2643,7 +1789,7 @@
       <c r="H29" s="7"/>
       <c r="I29" s="7"/>
     </row>
-    <row r="30" s="2" customFormat="1" spans="1:9">
+    <row r="30" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6"/>
       <c r="B30" s="7"/>
       <c r="C30" s="6"/>
@@ -2654,7 +1800,7 @@
       <c r="H30" s="7"/>
       <c r="I30" s="7"/>
     </row>
-    <row r="31" s="2" customFormat="1" spans="1:9">
+    <row r="31" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="6"/>
       <c r="B31" s="7"/>
       <c r="C31" s="6"/>
@@ -2665,7 +1811,7 @@
       <c r="H31" s="7"/>
       <c r="I31" s="7"/>
     </row>
-    <row r="32" s="2" customFormat="1" spans="1:9">
+    <row r="32" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="6"/>
       <c r="B32" s="7"/>
       <c r="C32" s="6"/>
@@ -2676,7 +1822,7 @@
       <c r="H32" s="7"/>
       <c r="I32" s="7"/>
     </row>
-    <row r="33" s="2" customFormat="1" spans="1:9">
+    <row r="33" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="6"/>
       <c r="B33" s="7"/>
       <c r="C33" s="6"/>
@@ -2687,7 +1833,7 @@
       <c r="H33" s="7"/>
       <c r="I33" s="7"/>
     </row>
-    <row r="34" s="2" customFormat="1" spans="1:9">
+    <row r="34" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6"/>
       <c r="B34" s="7"/>
       <c r="C34" s="6"/>
@@ -2698,7 +1844,7 @@
       <c r="H34" s="7"/>
       <c r="I34" s="7"/>
     </row>
-    <row r="35" s="2" customFormat="1" spans="1:9">
+    <row r="35" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="6"/>
       <c r="B35" s="7"/>
       <c r="C35" s="6"/>
@@ -2709,7 +1855,7 @@
       <c r="H35" s="7"/>
       <c r="I35" s="7"/>
     </row>
-    <row r="36" s="2" customFormat="1" spans="1:9">
+    <row r="36" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="6"/>
       <c r="B36" s="7"/>
       <c r="C36" s="6"/>
@@ -2721,59 +1867,66 @@
       <c r="I36" s="7"/>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:I36"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="17.6"/>
+  <sheetFormatPr defaultColWidth="11.0234375" defaultRowHeight="17.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="8.5625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="15.625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="13.1875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="21.7638888888889" style="3" customWidth="1"/>
-    <col min="5" max="5" width="31.4722222222222" style="3" customWidth="1"/>
-    <col min="6" max="6" width="25.4652777777778" style="2" customWidth="1"/>
-    <col min="7" max="7" width="11" style="2"/>
-    <col min="8" max="8" width="15.3888888888889" style="3" customWidth="1"/>
-    <col min="9" max="9" width="19.3263888888889" style="3" customWidth="1"/>
-    <col min="10" max="16384" width="11" style="2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="15.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="13.19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="21.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="31.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="25.47"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="15.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="19.33"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="10" style="1" width="11"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="31" customHeight="1" spans="1:9">
-      <c r="A1" s="4" t="s">
+    <row r="1" s="5" customFormat="true" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" s="2" customFormat="1" ht="35" customHeight="1" spans="1:9">
+    <row r="2" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
         <v>43</v>
       </c>
@@ -2798,7 +1951,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="1" ht="40" customHeight="1" spans="1:9">
+    <row r="3" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
         <v>46</v>
       </c>
@@ -2819,7 +1972,7 @@
       <c r="H3" s="7"/>
       <c r="I3" s="7"/>
     </row>
-    <row r="4" s="2" customFormat="1" ht="40" customHeight="1" spans="1:9">
+    <row r="4" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
         <v>49</v>
       </c>
@@ -2834,7 +1987,7 @@
       <c r="H4" s="7"/>
       <c r="I4" s="7"/>
     </row>
-    <row r="5" s="2" customFormat="1" ht="38" customHeight="1" spans="1:9">
+    <row r="5" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
         <v>50</v>
       </c>
@@ -2849,7 +2002,7 @@
       <c r="H5" s="7"/>
       <c r="I5" s="7"/>
     </row>
-    <row r="6" s="2" customFormat="1" ht="38" customHeight="1" spans="1:9">
+    <row r="6" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="7"/>
       <c r="C6" s="6"/>
@@ -2862,7 +2015,7 @@
       <c r="H6" s="7"/>
       <c r="I6" s="7"/>
     </row>
-    <row r="7" s="2" customFormat="1" ht="38" customHeight="1" spans="1:9">
+    <row r="7" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6"/>
       <c r="B7" s="7"/>
       <c r="C7" s="6"/>
@@ -2875,7 +2028,7 @@
       <c r="H7" s="7"/>
       <c r="I7" s="7"/>
     </row>
-    <row r="8" s="2" customFormat="1" ht="44" customHeight="1" spans="1:9">
+    <row r="8" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6"/>
       <c r="B8" s="7"/>
       <c r="C8" s="6"/>
@@ -2888,7 +2041,7 @@
       <c r="H8" s="7"/>
       <c r="I8" s="7"/>
     </row>
-    <row r="9" s="2" customFormat="1" ht="62" customHeight="1" spans="1:9">
+    <row r="9" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6"/>
       <c r="B9" s="7"/>
       <c r="C9" s="6"/>
@@ -2903,7 +2056,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" s="2" customFormat="1" ht="62" customHeight="1" spans="1:9">
+    <row r="10" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6"/>
       <c r="B10" s="7"/>
       <c r="C10" s="6"/>
@@ -2922,7 +2075,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" s="2" customFormat="1" ht="58" customHeight="1" spans="1:9">
+    <row r="11" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6"/>
       <c r="B11" s="7"/>
       <c r="C11" s="6"/>
@@ -2933,7 +2086,7 @@
       <c r="H11" s="7"/>
       <c r="I11" s="7"/>
     </row>
-    <row r="12" s="2" customFormat="1" spans="1:9">
+    <row r="12" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6"/>
       <c r="B12" s="7"/>
       <c r="C12" s="6"/>
@@ -2944,7 +2097,7 @@
       <c r="H12" s="7"/>
       <c r="I12" s="7"/>
     </row>
-    <row r="13" s="2" customFormat="1" spans="1:9">
+    <row r="13" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6"/>
       <c r="B13" s="7"/>
       <c r="C13" s="6"/>
@@ -2955,7 +2108,7 @@
       <c r="H13" s="7"/>
       <c r="I13" s="7"/>
     </row>
-    <row r="14" s="2" customFormat="1" spans="1:9">
+    <row r="14" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6"/>
       <c r="B14" s="7"/>
       <c r="C14" s="6"/>
@@ -2966,7 +2119,7 @@
       <c r="H14" s="7"/>
       <c r="I14" s="7"/>
     </row>
-    <row r="15" s="2" customFormat="1" spans="1:9">
+    <row r="15" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6"/>
       <c r="B15" s="7"/>
       <c r="C15" s="6"/>
@@ -2977,7 +2130,7 @@
       <c r="H15" s="7"/>
       <c r="I15" s="7"/>
     </row>
-    <row r="16" s="2" customFormat="1" spans="1:9">
+    <row r="16" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6"/>
       <c r="B16" s="7"/>
       <c r="C16" s="6"/>
@@ -2988,7 +2141,7 @@
       <c r="H16" s="7"/>
       <c r="I16" s="7"/>
     </row>
-    <row r="17" s="2" customFormat="1" spans="1:9">
+    <row r="17" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6"/>
       <c r="B17" s="7"/>
       <c r="C17" s="6"/>
@@ -2999,7 +2152,7 @@
       <c r="H17" s="7"/>
       <c r="I17" s="7"/>
     </row>
-    <row r="18" s="2" customFormat="1" spans="1:9">
+    <row r="18" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6"/>
       <c r="B18" s="7"/>
       <c r="C18" s="6"/>
@@ -3010,7 +2163,7 @@
       <c r="H18" s="7"/>
       <c r="I18" s="7"/>
     </row>
-    <row r="19" s="2" customFormat="1" spans="1:9">
+    <row r="19" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6"/>
       <c r="B19" s="7"/>
       <c r="C19" s="6"/>
@@ -3021,7 +2174,7 @@
       <c r="H19" s="7"/>
       <c r="I19" s="7"/>
     </row>
-    <row r="20" s="2" customFormat="1" spans="1:9">
+    <row r="20" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6"/>
       <c r="B20" s="7"/>
       <c r="C20" s="6"/>
@@ -3032,7 +2185,7 @@
       <c r="H20" s="7"/>
       <c r="I20" s="7"/>
     </row>
-    <row r="21" s="2" customFormat="1" spans="1:9">
+    <row r="21" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6"/>
       <c r="B21" s="7"/>
       <c r="C21" s="6"/>
@@ -3043,7 +2196,7 @@
       <c r="H21" s="7"/>
       <c r="I21" s="7"/>
     </row>
-    <row r="22" s="2" customFormat="1" spans="1:9">
+    <row r="22" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6"/>
       <c r="B22" s="7"/>
       <c r="C22" s="6"/>
@@ -3054,7 +2207,7 @@
       <c r="H22" s="7"/>
       <c r="I22" s="7"/>
     </row>
-    <row r="23" s="2" customFormat="1" spans="1:9">
+    <row r="23" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6"/>
       <c r="B23" s="7"/>
       <c r="C23" s="6"/>
@@ -3065,7 +2218,7 @@
       <c r="H23" s="7"/>
       <c r="I23" s="7"/>
     </row>
-    <row r="24" s="2" customFormat="1" spans="1:9">
+    <row r="24" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6"/>
       <c r="B24" s="7"/>
       <c r="C24" s="6"/>
@@ -3076,7 +2229,7 @@
       <c r="H24" s="7"/>
       <c r="I24" s="7"/>
     </row>
-    <row r="25" s="2" customFormat="1" spans="1:9">
+    <row r="25" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6"/>
       <c r="B25" s="7"/>
       <c r="C25" s="6"/>
@@ -3087,7 +2240,7 @@
       <c r="H25" s="7"/>
       <c r="I25" s="7"/>
     </row>
-    <row r="26" s="2" customFormat="1" spans="1:9">
+    <row r="26" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6"/>
       <c r="B26" s="7"/>
       <c r="C26" s="6"/>
@@ -3098,7 +2251,7 @@
       <c r="H26" s="7"/>
       <c r="I26" s="7"/>
     </row>
-    <row r="27" s="2" customFormat="1" spans="1:9">
+    <row r="27" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6"/>
       <c r="B27" s="7"/>
       <c r="C27" s="6"/>
@@ -3109,7 +2262,7 @@
       <c r="H27" s="7"/>
       <c r="I27" s="7"/>
     </row>
-    <row r="28" s="2" customFormat="1" spans="1:9">
+    <row r="28" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6"/>
       <c r="B28" s="7"/>
       <c r="C28" s="6"/>
@@ -3120,7 +2273,7 @@
       <c r="H28" s="7"/>
       <c r="I28" s="7"/>
     </row>
-    <row r="29" s="2" customFormat="1" spans="1:9">
+    <row r="29" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6"/>
       <c r="B29" s="7"/>
       <c r="C29" s="6"/>
@@ -3131,7 +2284,7 @@
       <c r="H29" s="7"/>
       <c r="I29" s="7"/>
     </row>
-    <row r="30" s="2" customFormat="1" spans="1:9">
+    <row r="30" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6"/>
       <c r="B30" s="7"/>
       <c r="C30" s="6"/>
@@ -3142,7 +2295,7 @@
       <c r="H30" s="7"/>
       <c r="I30" s="7"/>
     </row>
-    <row r="31" s="2" customFormat="1" spans="1:9">
+    <row r="31" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="6"/>
       <c r="B31" s="7"/>
       <c r="C31" s="6"/>
@@ -3153,7 +2306,7 @@
       <c r="H31" s="7"/>
       <c r="I31" s="7"/>
     </row>
-    <row r="32" s="2" customFormat="1" spans="1:9">
+    <row r="32" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="6"/>
       <c r="B32" s="7"/>
       <c r="C32" s="6"/>
@@ -3164,7 +2317,7 @@
       <c r="H32" s="7"/>
       <c r="I32" s="7"/>
     </row>
-    <row r="33" s="2" customFormat="1" spans="1:9">
+    <row r="33" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="6"/>
       <c r="B33" s="7"/>
       <c r="C33" s="6"/>
@@ -3175,7 +2328,7 @@
       <c r="H33" s="7"/>
       <c r="I33" s="7"/>
     </row>
-    <row r="34" s="2" customFormat="1" spans="1:9">
+    <row r="34" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6"/>
       <c r="B34" s="7"/>
       <c r="C34" s="6"/>
@@ -3186,7 +2339,7 @@
       <c r="H34" s="7"/>
       <c r="I34" s="7"/>
     </row>
-    <row r="35" s="2" customFormat="1" spans="1:9">
+    <row r="35" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="6"/>
       <c r="B35" s="7"/>
       <c r="C35" s="6"/>
@@ -3197,7 +2350,7 @@
       <c r="H35" s="7"/>
       <c r="I35" s="7"/>
     </row>
-    <row r="36" s="2" customFormat="1" spans="1:9">
+    <row r="36" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="6"/>
       <c r="B36" s="7"/>
       <c r="C36" s="6"/>
@@ -3209,18 +2362,30 @@
       <c r="I36" s="7"/>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="17.6"/>
+  <sheetFormatPr defaultColWidth="8.90234375" defaultRowHeight="17.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/Test_Cases.xlsx
+++ b/Test_Cases.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -8,11 +8,11 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="DoRobot" sheetId="1" state="visible" r:id="rId2"/>
-    <sheet name="Remote" sheetId="2" state="visible" r:id="rId3"/>
-    <sheet name="PICO4" sheetId="3" state="visible" r:id="rId4"/>
-    <sheet name="DataCollection" sheetId="4" state="visible" r:id="rId5"/>
-    <sheet name="Sheet4" sheetId="5" state="visible" r:id="rId6"/>
+    <sheet name="DoRobot" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Remote" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="PICO4" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="DataCollection" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Sheet4" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">DoRobot!$A$1:$J$1</definedName>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="124">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -113,7 +113,34 @@
     <t xml:space="preserve">模型推理时机械臂运行时的抖动问题</t>
   </si>
   <si>
-    <t xml:space="preserve">机械臂运行时抖动频繁，影响动作美观，经初步判断可能由于chunk 边界突变或数据未滤波导致。通过减少预测步长、增加滤波函数或加入平滑方案可能得到改善，但还需要继续测试与调整</t>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">机械臂运行时抖动频繁，影响动作美观，经初步判断可能由于</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">chunk </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">边界突变或数据未滤波导致。通过减少预测步长、增加滤波函数或加入平滑方案可能得到改善，但还需要继续测试与调整</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">Major</t>
@@ -125,9 +152,541 @@
     <t xml:space="preserve">Q1004</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">26</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">pro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V1(2026-4-3)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">基于</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">x86</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">平台（个人</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">端），在</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">robodriver</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">中研发并集成</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">pico4 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">双臂遥操</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">piper</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（遥操</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">数据保存）。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">开发基于</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">x86</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">pico4 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">双臂遥操</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">piper(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">仅遥操</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">3.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">将该项目移植到香橙派</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">007</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">数据保存的目录得根据需要修改</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">香橙派检测不到</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">can</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，需要额外安装</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">gs_usb</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Critical</t>
+  </si>
+  <si>
     <t xml:space="preserve">Q1005</t>
   </si>
   <si>
+    <t xml:space="preserve">V1-mini</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">基于</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">x86</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">平台（个人</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">端），基于</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">XR-Robotoolkit</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">开发</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">pico</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">双臂遥操</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">gen72</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">七轴机械臂的奇异点多，考虑借鉴非线性优化替换</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">IK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">求解</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">Q1006</t>
   </si>
   <si>
@@ -339,9 +898,6 @@
   </si>
   <si>
     <t xml:space="preserve">Sensor disconnect after 45min continuous run </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Critical</t>
   </si>
   <si>
     <t xml:space="preserve">FAIL</t>
@@ -385,7 +941,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="yy\年m\月d\日"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="11">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
@@ -417,11 +973,29 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF000000"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="10.5"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="0"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="0"/>
     </font>
     <font>
       <sz val="12"/>
@@ -508,73 +1082,85 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -649,13 +1235,119 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+  <a:themeElements>
+    <a:clrScheme name="LibreOffice">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="000000"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="FFFFFF"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="18A303"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="0369A3"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A33E03"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8E03A3"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="C99C00"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="C9211E"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000EE"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="551A8B"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme>
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:J80"/>
-  <sheetFormatPr defaultColWidth="11.0234375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.02734375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.89"/>
@@ -715,13 +1407,13 @@
       <c r="D2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="8" t="s">
         <v>15</v>
       </c>
       <c r="H2" s="5" t="s">
@@ -747,13 +1439,13 @@
       <c r="D3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="8" t="s">
         <v>22</v>
       </c>
       <c r="H3" s="5" t="s">
@@ -777,13 +1469,13 @@
       <c r="D4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="8" t="s">
         <v>28</v>
       </c>
       <c r="H4" s="5" t="s">
@@ -794,814 +1486,848 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="45.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="81.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-    </row>
-    <row r="6" customFormat="false" ht="45.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="98" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
+      <c r="C6" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="J6" s="5"/>
     </row>
     <row r="7" customFormat="false" ht="45.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
       <c r="H7" s="5"/>
       <c r="I7" s="5"/>
       <c r="J7" s="5"/>
     </row>
     <row r="8" customFormat="false" ht="45.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
       <c r="H8" s="5"/>
       <c r="I8" s="5"/>
       <c r="J8" s="5"/>
     </row>
     <row r="9" customFormat="false" ht="45.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
       <c r="H9" s="5"/>
       <c r="I9" s="5"/>
       <c r="J9" s="5"/>
     </row>
     <row r="10" customFormat="false" ht="45.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="8"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="10"/>
       <c r="I10" s="5"/>
       <c r="J10" s="5"/>
     </row>
     <row r="11" customFormat="false" ht="45.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
       <c r="H11" s="5"/>
       <c r="I11" s="5"/>
       <c r="J11" s="5"/>
     </row>
     <row r="12" customFormat="false" ht="45.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
       <c r="J12" s="5"/>
     </row>
     <row r="13" customFormat="false" ht="45.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
     </row>
     <row r="14" customFormat="false" ht="45.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
       <c r="H14" s="5"/>
       <c r="I14" s="5"/>
       <c r="J14" s="5"/>
     </row>
     <row r="15" customFormat="false" ht="45.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
       <c r="J15" s="5"/>
     </row>
     <row r="16" customFormat="false" ht="45.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
       <c r="H16" s="5"/>
       <c r="I16" s="5"/>
       <c r="J16" s="5"/>
     </row>
     <row r="17" customFormat="false" ht="45.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
       <c r="H17" s="5"/>
       <c r="I17" s="5"/>
       <c r="J17" s="5"/>
     </row>
     <row r="18" customFormat="false" ht="45.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
       <c r="H18" s="5"/>
       <c r="I18" s="5"/>
       <c r="J18" s="5"/>
     </row>
     <row r="19" customFormat="false" ht="45.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
       <c r="H19" s="5"/>
       <c r="I19" s="5"/>
       <c r="J19" s="5"/>
     </row>
     <row r="20" customFormat="false" ht="45.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
       <c r="H20" s="5"/>
       <c r="I20" s="5"/>
       <c r="J20" s="5"/>
     </row>
     <row r="21" customFormat="false" ht="45.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
       <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
       <c r="H21" s="5"/>
       <c r="I21" s="5"/>
       <c r="J21" s="5"/>
     </row>
     <row r="22" customFormat="false" ht="45.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
       <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
       <c r="J22" s="5"/>
     </row>
     <row r="23" customFormat="false" ht="45.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
       <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
       <c r="H23" s="5"/>
       <c r="I23" s="5"/>
       <c r="J23" s="5"/>
     </row>
     <row r="24" customFormat="false" ht="45.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
       <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
       <c r="H24" s="5"/>
       <c r="I24" s="5"/>
       <c r="J24" s="5"/>
     </row>
     <row r="25" customFormat="false" ht="45.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
       <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
       <c r="H25" s="5"/>
       <c r="I25" s="5"/>
       <c r="J25" s="5"/>
     </row>
     <row r="26" customFormat="false" ht="45.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
       <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="8"/>
       <c r="H26" s="5"/>
       <c r="I26" s="5"/>
       <c r="J26" s="5"/>
     </row>
     <row r="27" customFormat="false" ht="45.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
       <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="7"/>
-      <c r="G27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="8"/>
+      <c r="G27" s="8"/>
       <c r="H27" s="5"/>
       <c r="I27" s="5"/>
       <c r="J27" s="5"/>
     </row>
     <row r="28" customFormat="false" ht="45.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
       <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="8"/>
       <c r="H28" s="5"/>
       <c r="I28" s="5"/>
       <c r="J28" s="5"/>
     </row>
     <row r="29" customFormat="false" ht="45.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
       <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="8"/>
       <c r="H29" s="5"/>
       <c r="I29" s="5"/>
       <c r="J29" s="5"/>
     </row>
     <row r="30" customFormat="false" ht="45.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
       <c r="D30" s="5"/>
-      <c r="E30" s="5"/>
-      <c r="F30" s="7"/>
-      <c r="G30" s="7"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="8"/>
       <c r="H30" s="5"/>
       <c r="I30" s="5"/>
       <c r="J30" s="5"/>
     </row>
     <row r="31" customFormat="false" ht="45.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5"/>
       <c r="D31" s="5"/>
-      <c r="E31" s="5"/>
-      <c r="F31" s="7"/>
-      <c r="G31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="8"/>
+      <c r="G31" s="8"/>
       <c r="H31" s="5"/>
       <c r="I31" s="5"/>
       <c r="J31" s="5"/>
     </row>
     <row r="32" customFormat="false" ht="45.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5"/>
       <c r="D32" s="5"/>
-      <c r="E32" s="5"/>
-      <c r="F32" s="7"/>
-      <c r="G32" s="7"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="8"/>
+      <c r="G32" s="8"/>
       <c r="H32" s="5"/>
       <c r="I32" s="5"/>
       <c r="J32" s="5"/>
     </row>
     <row r="33" customFormat="false" ht="45.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5"/>
       <c r="D33" s="5"/>
-      <c r="E33" s="5"/>
-      <c r="F33" s="7"/>
-      <c r="G33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="8"/>
+      <c r="G33" s="8"/>
       <c r="H33" s="5"/>
       <c r="I33" s="5"/>
       <c r="J33" s="5"/>
     </row>
     <row r="34" customFormat="false" ht="45.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5"/>
       <c r="D34" s="5"/>
-      <c r="E34" s="5"/>
-      <c r="F34" s="7"/>
-      <c r="G34" s="7"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="8"/>
+      <c r="G34" s="8"/>
       <c r="H34" s="5"/>
       <c r="I34" s="5"/>
       <c r="J34" s="5"/>
     </row>
     <row r="35" customFormat="false" ht="45.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5"/>
       <c r="D35" s="5"/>
-      <c r="E35" s="5"/>
-      <c r="F35" s="7"/>
-      <c r="G35" s="7"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="8"/>
+      <c r="G35" s="8"/>
       <c r="H35" s="5"/>
       <c r="I35" s="5"/>
       <c r="J35" s="5"/>
     </row>
     <row r="36" customFormat="false" ht="45.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5"/>
       <c r="D36" s="5"/>
-      <c r="E36" s="5"/>
-      <c r="F36" s="7"/>
-      <c r="G36" s="7"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="8"/>
+      <c r="G36" s="8"/>
       <c r="H36" s="5"/>
       <c r="I36" s="5"/>
       <c r="J36" s="5"/>
     </row>
     <row r="37" customFormat="false" ht="45.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="5" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5"/>
       <c r="D37" s="5"/>
-      <c r="E37" s="5"/>
-      <c r="F37" s="7"/>
-      <c r="G37" s="7"/>
+      <c r="E37" s="7"/>
+      <c r="F37" s="8"/>
+      <c r="G37" s="8"/>
       <c r="H37" s="5"/>
       <c r="I37" s="5"/>
       <c r="J37" s="5"/>
     </row>
     <row r="38" customFormat="false" ht="45.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5"/>
       <c r="D38" s="5"/>
-      <c r="E38" s="5"/>
-      <c r="F38" s="7"/>
-      <c r="G38" s="7"/>
+      <c r="E38" s="7"/>
+      <c r="F38" s="8"/>
+      <c r="G38" s="8"/>
       <c r="H38" s="5"/>
       <c r="I38" s="5"/>
       <c r="J38" s="5"/>
     </row>
     <row r="39" customFormat="false" ht="45.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5"/>
       <c r="D39" s="5"/>
-      <c r="E39" s="5"/>
-      <c r="F39" s="7"/>
-      <c r="G39" s="7"/>
+      <c r="E39" s="7"/>
+      <c r="F39" s="8"/>
+      <c r="G39" s="8"/>
       <c r="H39" s="5"/>
       <c r="I39" s="5"/>
       <c r="J39" s="5"/>
     </row>
     <row r="40" customFormat="false" ht="45.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5"/>
       <c r="D40" s="5"/>
-      <c r="E40" s="5"/>
-      <c r="F40" s="7"/>
-      <c r="G40" s="7"/>
+      <c r="E40" s="7"/>
+      <c r="F40" s="8"/>
+      <c r="G40" s="8"/>
       <c r="H40" s="5"/>
       <c r="I40" s="5"/>
       <c r="J40" s="5"/>
     </row>
     <row r="41" customFormat="false" ht="45.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5"/>
       <c r="D41" s="5"/>
-      <c r="E41" s="5"/>
-      <c r="F41" s="7"/>
-      <c r="G41" s="7"/>
+      <c r="E41" s="7"/>
+      <c r="F41" s="8"/>
+      <c r="G41" s="8"/>
       <c r="H41" s="5"/>
       <c r="I41" s="5"/>
       <c r="J41" s="5"/>
     </row>
     <row r="42" customFormat="false" ht="45.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5"/>
       <c r="D42" s="5"/>
-      <c r="E42" s="5"/>
-      <c r="F42" s="7"/>
-      <c r="G42" s="7"/>
+      <c r="E42" s="7"/>
+      <c r="F42" s="8"/>
+      <c r="G42" s="8"/>
       <c r="H42" s="5"/>
       <c r="I42" s="5"/>
       <c r="J42" s="5"/>
     </row>
     <row r="43" customFormat="false" ht="45.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5"/>
       <c r="D43" s="5"/>
-      <c r="E43" s="5"/>
-      <c r="F43" s="7"/>
-      <c r="G43" s="7"/>
+      <c r="E43" s="7"/>
+      <c r="F43" s="8"/>
+      <c r="G43" s="8"/>
       <c r="H43" s="5"/>
       <c r="I43" s="5"/>
       <c r="J43" s="5"/>
     </row>
     <row r="44" customFormat="false" ht="45.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5"/>
       <c r="D44" s="5"/>
-      <c r="E44" s="5"/>
-      <c r="F44" s="7"/>
-      <c r="G44" s="7"/>
+      <c r="E44" s="7"/>
+      <c r="F44" s="8"/>
+      <c r="G44" s="8"/>
       <c r="H44" s="5"/>
       <c r="I44" s="5"/>
       <c r="J44" s="5"/>
     </row>
     <row r="45" customFormat="false" ht="45.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="5" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5"/>
       <c r="D45" s="5"/>
-      <c r="E45" s="5"/>
-      <c r="F45" s="7"/>
-      <c r="G45" s="7"/>
-      <c r="H45" s="8"/>
+      <c r="E45" s="7"/>
+      <c r="F45" s="8"/>
+      <c r="G45" s="8"/>
+      <c r="H45" s="10"/>
       <c r="I45" s="5"/>
       <c r="J45" s="5"/>
     </row>
     <row r="46" customFormat="false" ht="45.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="5" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5"/>
       <c r="D46" s="5"/>
-      <c r="E46" s="5"/>
-      <c r="F46" s="7"/>
-      <c r="G46" s="7"/>
+      <c r="E46" s="7"/>
+      <c r="F46" s="8"/>
+      <c r="G46" s="8"/>
       <c r="H46" s="5"/>
       <c r="I46" s="5"/>
       <c r="J46" s="5"/>
     </row>
     <row r="47" customFormat="false" ht="45.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="5" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5"/>
       <c r="D47" s="5"/>
-      <c r="E47" s="5"/>
-      <c r="F47" s="7"/>
-      <c r="G47" s="7"/>
+      <c r="E47" s="7"/>
+      <c r="F47" s="8"/>
+      <c r="G47" s="8"/>
       <c r="H47" s="5"/>
       <c r="I47" s="5"/>
       <c r="J47" s="5"/>
     </row>
     <row r="48" customFormat="false" ht="45.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="5" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
       <c r="D48" s="5"/>
-      <c r="E48" s="5"/>
-      <c r="F48" s="7"/>
-      <c r="G48" s="7"/>
+      <c r="E48" s="7"/>
+      <c r="F48" s="8"/>
+      <c r="G48" s="8"/>
       <c r="H48" s="5"/>
       <c r="I48" s="5"/>
       <c r="J48" s="5"/>
     </row>
     <row r="49" customFormat="false" ht="45.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="5" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
       <c r="D49" s="5"/>
-      <c r="E49" s="5"/>
-      <c r="F49" s="7"/>
-      <c r="G49" s="7"/>
+      <c r="E49" s="7"/>
+      <c r="F49" s="8"/>
+      <c r="G49" s="8"/>
       <c r="H49" s="5"/>
       <c r="I49" s="5"/>
       <c r="J49" s="5"/>
     </row>
     <row r="50" customFormat="false" ht="45.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="5" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5"/>
       <c r="D50" s="5"/>
-      <c r="E50" s="5"/>
-      <c r="F50" s="7"/>
-      <c r="G50" s="7"/>
+      <c r="E50" s="7"/>
+      <c r="F50" s="8"/>
+      <c r="G50" s="8"/>
       <c r="H50" s="5"/>
       <c r="I50" s="5"/>
       <c r="J50" s="5"/>
     </row>
     <row r="51" customFormat="false" ht="45.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="5" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
       <c r="D51" s="5"/>
-      <c r="E51" s="5"/>
-      <c r="F51" s="7"/>
-      <c r="G51" s="7"/>
+      <c r="E51" s="7"/>
+      <c r="F51" s="8"/>
+      <c r="G51" s="8"/>
       <c r="H51" s="5"/>
       <c r="I51" s="5"/>
       <c r="J51" s="5"/>
     </row>
     <row r="52" customFormat="false" ht="45.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="5" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5"/>
       <c r="D52" s="5"/>
-      <c r="E52" s="5"/>
-      <c r="F52" s="7"/>
-      <c r="G52" s="7"/>
+      <c r="E52" s="7"/>
+      <c r="F52" s="8"/>
+      <c r="G52" s="8"/>
       <c r="H52" s="5"/>
       <c r="I52" s="5"/>
       <c r="J52" s="5"/>
     </row>
     <row r="53" customFormat="false" ht="45.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="5" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5"/>
       <c r="D53" s="5"/>
-      <c r="E53" s="5"/>
-      <c r="F53" s="7"/>
-      <c r="G53" s="7"/>
+      <c r="E53" s="7"/>
+      <c r="F53" s="8"/>
+      <c r="G53" s="8"/>
       <c r="H53" s="5"/>
       <c r="I53" s="5"/>
       <c r="J53" s="5"/>
     </row>
     <row r="54" customFormat="false" ht="45.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="5" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5"/>
       <c r="D54" s="5"/>
-      <c r="E54" s="5"/>
-      <c r="F54" s="7"/>
-      <c r="G54" s="7"/>
+      <c r="E54" s="7"/>
+      <c r="F54" s="8"/>
+      <c r="G54" s="8"/>
       <c r="H54" s="5"/>
       <c r="I54" s="5"/>
       <c r="J54" s="5"/>
     </row>
     <row r="55" customFormat="false" ht="45.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="5" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="B55" s="5"/>
       <c r="C55" s="5"/>
       <c r="D55" s="5"/>
-      <c r="E55" s="5"/>
-      <c r="F55" s="7"/>
-      <c r="G55" s="7"/>
+      <c r="E55" s="7"/>
+      <c r="F55" s="8"/>
+      <c r="G55" s="8"/>
       <c r="H55" s="5"/>
       <c r="I55" s="5"/>
       <c r="J55" s="5"/>
     </row>
     <row r="56" customFormat="false" ht="45.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="5" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
       <c r="D56" s="5"/>
-      <c r="E56" s="5"/>
-      <c r="F56" s="7"/>
-      <c r="G56" s="7"/>
+      <c r="E56" s="7"/>
+      <c r="F56" s="8"/>
+      <c r="G56" s="8"/>
       <c r="H56" s="5"/>
       <c r="I56" s="5"/>
       <c r="J56" s="5"/>
     </row>
     <row r="57" customFormat="false" ht="45.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="5" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="B57" s="5"/>
       <c r="C57" s="5"/>
       <c r="D57" s="5"/>
-      <c r="E57" s="5"/>
-      <c r="F57" s="7"/>
-      <c r="G57" s="7"/>
+      <c r="E57" s="7"/>
+      <c r="F57" s="8"/>
+      <c r="G57" s="8"/>
       <c r="H57" s="5"/>
       <c r="I57" s="5"/>
       <c r="J57" s="5"/>
     </row>
     <row r="58" customFormat="false" ht="45.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="5" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="B58" s="5"/>
       <c r="C58" s="5"/>
       <c r="D58" s="5"/>
-      <c r="E58" s="5"/>
-      <c r="F58" s="7"/>
-      <c r="G58" s="7"/>
+      <c r="E58" s="7"/>
+      <c r="F58" s="8"/>
+      <c r="G58" s="8"/>
       <c r="H58" s="5"/>
       <c r="I58" s="5"/>
       <c r="J58" s="5"/>
     </row>
     <row r="59" customFormat="false" ht="45.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="5" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
       <c r="D59" s="5"/>
-      <c r="E59" s="5"/>
-      <c r="F59" s="7"/>
-      <c r="G59" s="7"/>
+      <c r="E59" s="7"/>
+      <c r="F59" s="8"/>
+      <c r="G59" s="8"/>
       <c r="H59" s="5"/>
       <c r="I59" s="5"/>
       <c r="J59" s="5"/>
     </row>
     <row r="60" customFormat="false" ht="45.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="5" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
       <c r="D60" s="5"/>
-      <c r="E60" s="5"/>
-      <c r="F60" s="7"/>
-      <c r="G60" s="7"/>
+      <c r="E60" s="7"/>
+      <c r="F60" s="8"/>
+      <c r="G60" s="8"/>
       <c r="H60" s="5"/>
       <c r="I60" s="5"/>
       <c r="J60" s="5"/>
     </row>
     <row r="61" customFormat="false" ht="45.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="5" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
       <c r="D61" s="5"/>
-      <c r="E61" s="5"/>
-      <c r="F61" s="7"/>
-      <c r="G61" s="7"/>
+      <c r="E61" s="7"/>
+      <c r="F61" s="8"/>
+      <c r="G61" s="8"/>
       <c r="H61" s="5"/>
       <c r="I61" s="5"/>
       <c r="J61" s="5"/>
     </row>
     <row r="62" customFormat="false" ht="45.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="5" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="B62" s="5"/>
       <c r="C62" s="5"/>
       <c r="D62" s="5"/>
-      <c r="E62" s="5"/>
-      <c r="F62" s="7"/>
-      <c r="G62" s="7"/>
+      <c r="E62" s="7"/>
+      <c r="F62" s="8"/>
+      <c r="G62" s="8"/>
       <c r="H62" s="5"/>
       <c r="I62" s="5"/>
       <c r="J62" s="5"/>
@@ -1609,221 +2335,221 @@
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="4"/>
       <c r="B63" s="4"/>
-      <c r="C63" s="9"/>
+      <c r="C63" s="11"/>
       <c r="D63" s="4"/>
-      <c r="E63" s="9"/>
-      <c r="F63" s="10"/>
-      <c r="G63" s="11"/>
+      <c r="E63" s="11"/>
+      <c r="F63" s="12"/>
+      <c r="G63" s="13"/>
       <c r="H63" s="4"/>
-      <c r="I63" s="9"/>
-      <c r="J63" s="9"/>
+      <c r="I63" s="11"/>
+      <c r="J63" s="11"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="4"/>
       <c r="B64" s="4"/>
-      <c r="C64" s="9"/>
+      <c r="C64" s="11"/>
       <c r="D64" s="4"/>
-      <c r="E64" s="9"/>
-      <c r="F64" s="10"/>
-      <c r="G64" s="11"/>
+      <c r="E64" s="11"/>
+      <c r="F64" s="12"/>
+      <c r="G64" s="13"/>
       <c r="H64" s="4"/>
-      <c r="I64" s="9"/>
-      <c r="J64" s="9"/>
+      <c r="I64" s="11"/>
+      <c r="J64" s="11"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="4"/>
       <c r="B65" s="4"/>
-      <c r="C65" s="9"/>
+      <c r="C65" s="11"/>
       <c r="D65" s="4"/>
-      <c r="E65" s="9"/>
-      <c r="F65" s="10"/>
-      <c r="G65" s="11"/>
+      <c r="E65" s="11"/>
+      <c r="F65" s="12"/>
+      <c r="G65" s="13"/>
       <c r="H65" s="4"/>
-      <c r="I65" s="9"/>
-      <c r="J65" s="9"/>
+      <c r="I65" s="11"/>
+      <c r="J65" s="11"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="4"/>
       <c r="B66" s="4"/>
-      <c r="C66" s="9"/>
+      <c r="C66" s="11"/>
       <c r="D66" s="4"/>
-      <c r="E66" s="9"/>
-      <c r="F66" s="10"/>
-      <c r="G66" s="11"/>
+      <c r="E66" s="11"/>
+      <c r="F66" s="12"/>
+      <c r="G66" s="13"/>
       <c r="H66" s="4"/>
-      <c r="I66" s="9"/>
-      <c r="J66" s="9"/>
+      <c r="I66" s="11"/>
+      <c r="J66" s="11"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="4"/>
       <c r="B67" s="4"/>
-      <c r="C67" s="9"/>
+      <c r="C67" s="11"/>
       <c r="D67" s="4"/>
-      <c r="E67" s="9"/>
-      <c r="F67" s="10"/>
-      <c r="G67" s="11"/>
+      <c r="E67" s="11"/>
+      <c r="F67" s="12"/>
+      <c r="G67" s="13"/>
       <c r="H67" s="4"/>
-      <c r="I67" s="9"/>
-      <c r="J67" s="9"/>
+      <c r="I67" s="11"/>
+      <c r="J67" s="11"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="4"/>
       <c r="B68" s="4"/>
-      <c r="C68" s="9"/>
+      <c r="C68" s="11"/>
       <c r="D68" s="4"/>
-      <c r="E68" s="9"/>
-      <c r="F68" s="10"/>
-      <c r="G68" s="11"/>
+      <c r="E68" s="11"/>
+      <c r="F68" s="12"/>
+      <c r="G68" s="13"/>
       <c r="H68" s="4"/>
-      <c r="I68" s="9"/>
-      <c r="J68" s="9"/>
+      <c r="I68" s="11"/>
+      <c r="J68" s="11"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="4"/>
       <c r="B69" s="4"/>
-      <c r="C69" s="9"/>
+      <c r="C69" s="11"/>
       <c r="D69" s="4"/>
-      <c r="E69" s="9"/>
-      <c r="F69" s="10"/>
-      <c r="G69" s="11"/>
+      <c r="E69" s="11"/>
+      <c r="F69" s="12"/>
+      <c r="G69" s="13"/>
       <c r="H69" s="4"/>
-      <c r="I69" s="9"/>
-      <c r="J69" s="9"/>
+      <c r="I69" s="11"/>
+      <c r="J69" s="11"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="4"/>
       <c r="B70" s="4"/>
-      <c r="C70" s="9"/>
+      <c r="C70" s="11"/>
       <c r="D70" s="4"/>
-      <c r="E70" s="9"/>
-      <c r="F70" s="10"/>
-      <c r="G70" s="11"/>
+      <c r="E70" s="11"/>
+      <c r="F70" s="12"/>
+      <c r="G70" s="13"/>
       <c r="H70" s="4"/>
-      <c r="I70" s="9"/>
-      <c r="J70" s="9"/>
+      <c r="I70" s="11"/>
+      <c r="J70" s="11"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="4"/>
       <c r="B71" s="4"/>
-      <c r="C71" s="9"/>
+      <c r="C71" s="11"/>
       <c r="D71" s="4"/>
-      <c r="E71" s="9"/>
-      <c r="F71" s="10"/>
-      <c r="G71" s="11"/>
+      <c r="E71" s="11"/>
+      <c r="F71" s="12"/>
+      <c r="G71" s="13"/>
       <c r="H71" s="4"/>
-      <c r="I71" s="9"/>
-      <c r="J71" s="9"/>
+      <c r="I71" s="11"/>
+      <c r="J71" s="11"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="4"/>
       <c r="B72" s="4"/>
-      <c r="C72" s="9"/>
+      <c r="C72" s="11"/>
       <c r="D72" s="4"/>
-      <c r="E72" s="9"/>
-      <c r="F72" s="10"/>
-      <c r="G72" s="11"/>
+      <c r="E72" s="11"/>
+      <c r="F72" s="12"/>
+      <c r="G72" s="13"/>
       <c r="H72" s="4"/>
-      <c r="I72" s="9"/>
-      <c r="J72" s="9"/>
+      <c r="I72" s="11"/>
+      <c r="J72" s="11"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="4"/>
       <c r="B73" s="4"/>
-      <c r="C73" s="9"/>
+      <c r="C73" s="11"/>
       <c r="D73" s="4"/>
-      <c r="E73" s="9"/>
-      <c r="F73" s="9"/>
+      <c r="E73" s="11"/>
+      <c r="F73" s="11"/>
       <c r="G73" s="4"/>
       <c r="H73" s="4"/>
-      <c r="I73" s="9"/>
-      <c r="J73" s="9"/>
+      <c r="I73" s="11"/>
+      <c r="J73" s="11"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="4"/>
       <c r="B74" s="4"/>
-      <c r="C74" s="9"/>
+      <c r="C74" s="11"/>
       <c r="D74" s="4"/>
-      <c r="E74" s="9"/>
-      <c r="F74" s="9"/>
+      <c r="E74" s="11"/>
+      <c r="F74" s="11"/>
       <c r="G74" s="4"/>
       <c r="H74" s="4"/>
-      <c r="I74" s="9"/>
-      <c r="J74" s="9"/>
+      <c r="I74" s="11"/>
+      <c r="J74" s="11"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="4"/>
       <c r="B75" s="4"/>
-      <c r="C75" s="9"/>
+      <c r="C75" s="11"/>
       <c r="D75" s="4"/>
-      <c r="E75" s="9"/>
-      <c r="F75" s="9"/>
+      <c r="E75" s="11"/>
+      <c r="F75" s="11"/>
       <c r="G75" s="4"/>
       <c r="H75" s="4"/>
-      <c r="I75" s="9"/>
-      <c r="J75" s="9"/>
+      <c r="I75" s="11"/>
+      <c r="J75" s="11"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="4"/>
       <c r="B76" s="4"/>
-      <c r="C76" s="9"/>
+      <c r="C76" s="11"/>
       <c r="D76" s="4"/>
-      <c r="E76" s="9"/>
-      <c r="F76" s="9"/>
+      <c r="E76" s="11"/>
+      <c r="F76" s="11"/>
       <c r="G76" s="4"/>
       <c r="H76" s="4"/>
-      <c r="I76" s="9"/>
-      <c r="J76" s="9"/>
+      <c r="I76" s="11"/>
+      <c r="J76" s="11"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="4"/>
       <c r="B77" s="4"/>
-      <c r="C77" s="9"/>
+      <c r="C77" s="11"/>
       <c r="D77" s="4"/>
-      <c r="E77" s="9"/>
-      <c r="F77" s="9"/>
+      <c r="E77" s="11"/>
+      <c r="F77" s="11"/>
       <c r="G77" s="4"/>
       <c r="H77" s="4"/>
-      <c r="I77" s="9"/>
-      <c r="J77" s="9"/>
+      <c r="I77" s="11"/>
+      <c r="J77" s="11"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="4"/>
       <c r="B78" s="4"/>
-      <c r="C78" s="9"/>
+      <c r="C78" s="11"/>
       <c r="D78" s="4"/>
-      <c r="E78" s="9"/>
-      <c r="F78" s="9"/>
+      <c r="E78" s="11"/>
+      <c r="F78" s="11"/>
       <c r="G78" s="4"/>
       <c r="H78" s="4"/>
-      <c r="I78" s="9"/>
-      <c r="J78" s="9"/>
+      <c r="I78" s="11"/>
+      <c r="J78" s="11"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="4"/>
       <c r="B79" s="4"/>
-      <c r="C79" s="9"/>
+      <c r="C79" s="11"/>
       <c r="D79" s="4"/>
-      <c r="E79" s="9"/>
-      <c r="F79" s="9"/>
+      <c r="E79" s="11"/>
+      <c r="F79" s="11"/>
       <c r="G79" s="4"/>
       <c r="H79" s="4"/>
-      <c r="I79" s="9"/>
-      <c r="J79" s="9"/>
+      <c r="I79" s="11"/>
+      <c r="J79" s="11"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="4"/>
       <c r="B80" s="4"/>
-      <c r="C80" s="9"/>
+      <c r="C80" s="11"/>
       <c r="D80" s="4"/>
-      <c r="E80" s="9"/>
-      <c r="F80" s="9"/>
+      <c r="E80" s="11"/>
+      <c r="F80" s="11"/>
       <c r="G80" s="4"/>
       <c r="H80" s="4"/>
-      <c r="I80" s="9"/>
-      <c r="J80" s="9"/>
+      <c r="I80" s="11"/>
+      <c r="J80" s="11"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:J2 A5:J62 A3:C4 E3:J4">
+  <conditionalFormatting sqref="A2:J2 A3:C4 E3:J4 A7:J62 A5:E5 G5:J6 A6 E6 C6">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -1853,12 +2579,42 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="6">
+  <conditionalFormatting sqref="F5:F6">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFDEE6EF"/>
+        <color rgb="FFFFD8CE"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFDEE6EF"/>
+        <color rgb="FFFFD8CE"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D6">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFDEE6EF"/>
+        <color rgb="FFFFD8CE"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="9">
     <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="J1:J1062" type="list">
       <formula1>"PASS,PASS*,DEFERRED,PASS with workaround"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E1 E3:E36 E38:E1062" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E1 E3:E4 E6:E36 E38:E1062" type="list">
       <formula1>"设备的连接与稳定性,运行时的鲁棒性,性能观测结果,硬件,软件,"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -1874,7 +2630,19 @@
       <formula1>"Critical,Major,Minor,None"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C1:C1062" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C1:C4 C7:C1062" type="list">
+      <formula1>"Nano,V1-mini,V1-plug,V2-mini,V2-plug,V2-max"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E5" type="list">
+      <formula1>"设备的连接与稳定性,运行时的鲁棒性,性能观测结果,硬件,软件,开发,"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C5" type="list">
+      <formula1>"Nano,V1-mini,V1-plug,V2-mini,V2-plug,V2-max,pro"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C6" type="list">
       <formula1>"Nano,V1-mini,V1-plug,V2-mini,V2-plug,V2-max"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -1890,12 +2658,12 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I35"/>
-  <sheetFormatPr defaultColWidth="11.0234375" defaultRowHeight="17.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.02734375" defaultRowHeight="17.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="15.63"/>
@@ -1910,457 +2678,457 @@
   </cols>
   <sheetData>
     <row r="1" s="4" customFormat="true" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="15" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="B2" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="C2" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="D2" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="E2" s="15"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
+      <c r="A2" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="E2" s="17"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
     </row>
     <row r="3" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="C3" s="14"/>
-      <c r="D3" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="E3" s="15"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
-      <c r="H3" s="15"/>
-      <c r="I3" s="15"/>
+      <c r="A3" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="C3" s="16"/>
+      <c r="D3" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="E3" s="17"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="17"/>
     </row>
     <row r="4" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="B4" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="C4" s="14"/>
-      <c r="D4" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="E4" s="15"/>
-      <c r="F4" s="14"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="15"/>
-      <c r="I4" s="15"/>
+      <c r="B4" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="C4" s="16"/>
+      <c r="D4" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="E4" s="17"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
     </row>
     <row r="5" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="14"/>
-      <c r="B5" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="C5" s="14"/>
-      <c r="D5" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="E5" s="15"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14"/>
-      <c r="H5" s="15"/>
-      <c r="I5" s="15"/>
+      <c r="A5" s="16"/>
+      <c r="B5" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="C5" s="16"/>
+      <c r="D5" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="E5" s="17"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="17"/>
+      <c r="I5" s="17"/>
     </row>
     <row r="6" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="14"/>
-      <c r="B6" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="C6" s="14"/>
-      <c r="D6" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="E6" s="15"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14"/>
-      <c r="H6" s="15"/>
-      <c r="I6" s="15"/>
+      <c r="A6" s="16"/>
+      <c r="B6" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="C6" s="16"/>
+      <c r="D6" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="E6" s="17"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
     </row>
     <row r="7" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="14"/>
-      <c r="B7" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="C7" s="14"/>
-      <c r="D7" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="E7" s="15"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="15"/>
-      <c r="I7" s="15"/>
+      <c r="A7" s="16"/>
+      <c r="B7" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="C7" s="16"/>
+      <c r="D7" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="E7" s="17"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="17"/>
+      <c r="I7" s="17"/>
     </row>
     <row r="8" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="14"/>
-      <c r="B8" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="C8" s="14"/>
-      <c r="D8" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="E8" s="15"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="15" t="s">
+      <c r="A8" s="16"/>
+      <c r="B8" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="C8" s="16"/>
+      <c r="D8" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="E8" s="17"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="17" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="14"/>
-      <c r="B9" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="C9" s="14"/>
-      <c r="D9" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="E9" s="15" t="s">
-        <v>98</v>
-      </c>
-      <c r="F9" s="14"/>
-      <c r="G9" s="16" t="s">
+      <c r="A9" s="16"/>
+      <c r="B9" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="C9" s="16"/>
+      <c r="D9" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="F9" s="16"/>
+      <c r="G9" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="H9" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="I9" s="15" t="s">
+      <c r="H9" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="I9" s="17" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="14"/>
-      <c r="B10" s="15"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="15"/>
-      <c r="I10" s="15"/>
+      <c r="A10" s="16"/>
+      <c r="B10" s="17"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="17"/>
+      <c r="I10" s="17"/>
     </row>
     <row r="11" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="14"/>
-      <c r="B11" s="15"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="15"/>
-      <c r="I11" s="15"/>
+      <c r="A11" s="16"/>
+      <c r="B11" s="17"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="17"/>
+      <c r="I11" s="17"/>
     </row>
     <row r="12" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="14"/>
-      <c r="B12" s="15"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="15"/>
-      <c r="I12" s="15"/>
+      <c r="A12" s="16"/>
+      <c r="B12" s="17"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="17"/>
     </row>
     <row r="13" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="14"/>
-      <c r="B13" s="15"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="15"/>
-      <c r="I13" s="15"/>
+      <c r="A13" s="16"/>
+      <c r="B13" s="17"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="17"/>
+      <c r="I13" s="17"/>
     </row>
     <row r="14" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="14"/>
-      <c r="B14" s="15"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="15"/>
-      <c r="I14" s="15"/>
+      <c r="A14" s="16"/>
+      <c r="B14" s="17"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="17"/>
+      <c r="I14" s="17"/>
     </row>
     <row r="15" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="14"/>
-      <c r="B15" s="15"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="15"/>
-      <c r="I15" s="15"/>
+      <c r="A15" s="16"/>
+      <c r="B15" s="17"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="17"/>
+      <c r="I15" s="17"/>
     </row>
     <row r="16" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="14"/>
-      <c r="B16" s="15"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="15"/>
-      <c r="I16" s="15"/>
+      <c r="A16" s="16"/>
+      <c r="B16" s="17"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="17"/>
+      <c r="I16" s="17"/>
     </row>
     <row r="17" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="14"/>
-      <c r="B17" s="15"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="15"/>
-      <c r="I17" s="15"/>
+      <c r="A17" s="16"/>
+      <c r="B17" s="17"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="17"/>
+      <c r="I17" s="17"/>
     </row>
     <row r="18" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="14"/>
-      <c r="B18" s="15"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="15"/>
-      <c r="I18" s="15"/>
+      <c r="A18" s="16"/>
+      <c r="B18" s="17"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="16"/>
+      <c r="H18" s="17"/>
+      <c r="I18" s="17"/>
     </row>
     <row r="19" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="14"/>
-      <c r="B19" s="15"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="15"/>
-      <c r="I19" s="15"/>
+      <c r="A19" s="16"/>
+      <c r="B19" s="17"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="16"/>
+      <c r="H19" s="17"/>
+      <c r="I19" s="17"/>
     </row>
     <row r="20" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="14"/>
-      <c r="B20" s="15"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="15"/>
-      <c r="I20" s="15"/>
+      <c r="A20" s="16"/>
+      <c r="B20" s="17"/>
+      <c r="C20" s="16"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="17"/>
+      <c r="F20" s="16"/>
+      <c r="G20" s="16"/>
+      <c r="H20" s="17"/>
+      <c r="I20" s="17"/>
     </row>
     <row r="21" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="14"/>
-      <c r="B21" s="15"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="15"/>
-      <c r="I21" s="15"/>
+      <c r="A21" s="16"/>
+      <c r="B21" s="17"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="16"/>
+      <c r="H21" s="17"/>
+      <c r="I21" s="17"/>
     </row>
     <row r="22" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="14"/>
-      <c r="B22" s="15"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="15"/>
-      <c r="I22" s="15"/>
+      <c r="A22" s="16"/>
+      <c r="B22" s="17"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="16"/>
+      <c r="H22" s="17"/>
+      <c r="I22" s="17"/>
     </row>
     <row r="23" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="14"/>
-      <c r="B23" s="15"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="15"/>
-      <c r="I23" s="15"/>
+      <c r="A23" s="16"/>
+      <c r="B23" s="17"/>
+      <c r="C23" s="16"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="16"/>
+      <c r="G23" s="16"/>
+      <c r="H23" s="17"/>
+      <c r="I23" s="17"/>
     </row>
     <row r="24" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="14"/>
-      <c r="B24" s="15"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="15"/>
-      <c r="I24" s="15"/>
+      <c r="A24" s="16"/>
+      <c r="B24" s="17"/>
+      <c r="C24" s="16"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="17"/>
+      <c r="F24" s="16"/>
+      <c r="G24" s="16"/>
+      <c r="H24" s="17"/>
+      <c r="I24" s="17"/>
     </row>
     <row r="25" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="14"/>
-      <c r="B25" s="15"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="15"/>
-      <c r="I25" s="15"/>
+      <c r="A25" s="16"/>
+      <c r="B25" s="17"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="16"/>
+      <c r="G25" s="16"/>
+      <c r="H25" s="17"/>
+      <c r="I25" s="17"/>
     </row>
     <row r="26" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="14"/>
-      <c r="B26" s="15"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="15"/>
-      <c r="I26" s="15"/>
+      <c r="A26" s="16"/>
+      <c r="B26" s="17"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="17"/>
+      <c r="F26" s="16"/>
+      <c r="G26" s="16"/>
+      <c r="H26" s="17"/>
+      <c r="I26" s="17"/>
     </row>
     <row r="27" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="14"/>
-      <c r="B27" s="15"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="15"/>
-      <c r="I27" s="15"/>
+      <c r="A27" s="16"/>
+      <c r="B27" s="17"/>
+      <c r="C27" s="16"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="16"/>
+      <c r="G27" s="16"/>
+      <c r="H27" s="17"/>
+      <c r="I27" s="17"/>
     </row>
     <row r="28" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="14"/>
-      <c r="B28" s="15"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="15"/>
-      <c r="I28" s="15"/>
+      <c r="A28" s="16"/>
+      <c r="B28" s="17"/>
+      <c r="C28" s="16"/>
+      <c r="D28" s="17"/>
+      <c r="E28" s="17"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="16"/>
+      <c r="H28" s="17"/>
+      <c r="I28" s="17"/>
     </row>
     <row r="29" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="14"/>
-      <c r="B29" s="15"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="15"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="15"/>
-      <c r="I29" s="15"/>
+      <c r="A29" s="16"/>
+      <c r="B29" s="17"/>
+      <c r="C29" s="16"/>
+      <c r="D29" s="17"/>
+      <c r="E29" s="17"/>
+      <c r="F29" s="16"/>
+      <c r="G29" s="16"/>
+      <c r="H29" s="17"/>
+      <c r="I29" s="17"/>
     </row>
     <row r="30" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="14"/>
-      <c r="B30" s="15"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="15"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="15"/>
-      <c r="I30" s="15"/>
+      <c r="A30" s="16"/>
+      <c r="B30" s="17"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="17"/>
+      <c r="E30" s="17"/>
+      <c r="F30" s="16"/>
+      <c r="G30" s="16"/>
+      <c r="H30" s="17"/>
+      <c r="I30" s="17"/>
     </row>
     <row r="31" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="14"/>
-      <c r="B31" s="15"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="15"/>
-      <c r="I31" s="15"/>
+      <c r="A31" s="16"/>
+      <c r="B31" s="17"/>
+      <c r="C31" s="16"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="17"/>
+      <c r="F31" s="16"/>
+      <c r="G31" s="16"/>
+      <c r="H31" s="17"/>
+      <c r="I31" s="17"/>
     </row>
     <row r="32" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="14"/>
-      <c r="B32" s="15"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="15"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="15"/>
-      <c r="I32" s="15"/>
+      <c r="A32" s="16"/>
+      <c r="B32" s="17"/>
+      <c r="C32" s="16"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="17"/>
+      <c r="F32" s="16"/>
+      <c r="G32" s="16"/>
+      <c r="H32" s="17"/>
+      <c r="I32" s="17"/>
     </row>
     <row r="33" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="14"/>
-      <c r="B33" s="15"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="15"/>
-      <c r="E33" s="15"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="15"/>
-      <c r="I33" s="15"/>
+      <c r="A33" s="16"/>
+      <c r="B33" s="17"/>
+      <c r="C33" s="16"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="17"/>
+      <c r="F33" s="16"/>
+      <c r="G33" s="16"/>
+      <c r="H33" s="17"/>
+      <c r="I33" s="17"/>
     </row>
     <row r="34" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="14"/>
-      <c r="B34" s="15"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="15"/>
-      <c r="E34" s="15"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="15"/>
-      <c r="I34" s="15"/>
+      <c r="A34" s="16"/>
+      <c r="B34" s="17"/>
+      <c r="C34" s="16"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="17"/>
+      <c r="F34" s="16"/>
+      <c r="G34" s="16"/>
+      <c r="H34" s="17"/>
+      <c r="I34" s="17"/>
     </row>
     <row r="35" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="14"/>
-      <c r="B35" s="15"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="15"/>
-      <c r="E35" s="15"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="15"/>
-      <c r="I35" s="15"/>
+      <c r="A35" s="16"/>
+      <c r="B35" s="17"/>
+      <c r="C35" s="16"/>
+      <c r="D35" s="17"/>
+      <c r="E35" s="17"/>
+      <c r="F35" s="16"/>
+      <c r="G35" s="16"/>
+      <c r="H35" s="17"/>
+      <c r="I35" s="17"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2374,12 +3142,12 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I36"/>
-  <sheetFormatPr defaultColWidth="11.0234375" defaultRowHeight="17.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.02734375" defaultRowHeight="17.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="15.63"/>
@@ -2394,504 +3162,504 @@
   </cols>
   <sheetData>
     <row r="1" s="4" customFormat="true" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="15" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="E2" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="C3" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="D3" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="C2" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="D2" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="E2" s="15" t="s">
+      <c r="E3" s="17"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="17"/>
+    </row>
+    <row r="4" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="C4" s="16"/>
+      <c r="D4" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14" t="s">
+      <c r="E4" s="17"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
+    </row>
+    <row r="5" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="C5" s="16"/>
+      <c r="D5" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="E5" s="17"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="17"/>
+      <c r="I5" s="17"/>
+    </row>
+    <row r="6" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="C6" s="16"/>
+      <c r="D6" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15" t="s">
+      <c r="E6" s="17"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
+    </row>
+    <row r="7" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="C7" s="16"/>
+      <c r="D7" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="E7" s="17"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="17"/>
+      <c r="I7" s="17"/>
+    </row>
+    <row r="8" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="C8" s="16"/>
+      <c r="D8" s="17" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="14" t="s">
+      <c r="E8" s="17"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="17"/>
+    </row>
+    <row r="9" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="C9" s="16"/>
+      <c r="D9" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="E9" s="17"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="17" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="C10" s="16"/>
+      <c r="D10" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="B3" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="C3" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="E3" s="15"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
-      <c r="H3" s="15"/>
-      <c r="I3" s="15"/>
-    </row>
-    <row r="4" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="C4" s="14"/>
-      <c r="D4" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="E4" s="15"/>
-      <c r="F4" s="14"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="15"/>
-      <c r="I4" s="15"/>
-    </row>
-    <row r="5" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="C5" s="14"/>
-      <c r="D5" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="E5" s="15"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14"/>
-      <c r="H5" s="15"/>
-      <c r="I5" s="15"/>
-    </row>
-    <row r="6" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="B6" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="C6" s="14"/>
-      <c r="D6" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="E6" s="15"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14"/>
-      <c r="H6" s="15"/>
-      <c r="I6" s="15"/>
-    </row>
-    <row r="7" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="B7" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="C7" s="14"/>
-      <c r="D7" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="E7" s="15"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="15"/>
-      <c r="I7" s="15"/>
-    </row>
-    <row r="8" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="B8" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="C8" s="14"/>
-      <c r="D8" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="E8" s="15"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="15"/>
-    </row>
-    <row r="9" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="B9" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="C9" s="14"/>
-      <c r="D9" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="E9" s="15"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="15" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="B10" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="C10" s="14"/>
-      <c r="D10" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="E10" s="15" t="s">
-        <v>98</v>
-      </c>
-      <c r="F10" s="14"/>
-      <c r="G10" s="16" t="s">
+      <c r="E10" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="F10" s="16"/>
+      <c r="G10" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="H10" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="I10" s="15" t="s">
+      <c r="H10" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="I10" s="17" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="B11" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="D11" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="E11" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="15"/>
-      <c r="I11" s="15" t="s">
+      <c r="A11" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="D11" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="17"/>
+      <c r="I11" s="17" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="14"/>
-      <c r="B12" s="15"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="15"/>
-      <c r="I12" s="15"/>
+      <c r="A12" s="16"/>
+      <c r="B12" s="17"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="17"/>
     </row>
     <row r="13" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="14"/>
-      <c r="B13" s="15"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="15"/>
-      <c r="I13" s="15"/>
+      <c r="A13" s="16"/>
+      <c r="B13" s="17"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="17"/>
+      <c r="I13" s="17"/>
     </row>
     <row r="14" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="14"/>
-      <c r="B14" s="15"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="15"/>
-      <c r="I14" s="15"/>
+      <c r="A14" s="16"/>
+      <c r="B14" s="17"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="17"/>
+      <c r="I14" s="17"/>
     </row>
     <row r="15" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="14"/>
-      <c r="B15" s="15"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="15"/>
-      <c r="I15" s="15"/>
+      <c r="A15" s="16"/>
+      <c r="B15" s="17"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="17"/>
+      <c r="I15" s="17"/>
     </row>
     <row r="16" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="14"/>
-      <c r="B16" s="15"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="15"/>
-      <c r="I16" s="15"/>
+      <c r="A16" s="16"/>
+      <c r="B16" s="17"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="17"/>
+      <c r="I16" s="17"/>
     </row>
     <row r="17" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="14"/>
-      <c r="B17" s="15"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="15"/>
-      <c r="I17" s="15"/>
+      <c r="A17" s="16"/>
+      <c r="B17" s="17"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="17"/>
+      <c r="I17" s="17"/>
     </row>
     <row r="18" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="14"/>
-      <c r="B18" s="15"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="15"/>
-      <c r="I18" s="15"/>
+      <c r="A18" s="16"/>
+      <c r="B18" s="17"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="16"/>
+      <c r="H18" s="17"/>
+      <c r="I18" s="17"/>
     </row>
     <row r="19" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="14"/>
-      <c r="B19" s="15"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="15"/>
-      <c r="I19" s="15"/>
+      <c r="A19" s="16"/>
+      <c r="B19" s="17"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="16"/>
+      <c r="H19" s="17"/>
+      <c r="I19" s="17"/>
     </row>
     <row r="20" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="14"/>
-      <c r="B20" s="15"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="15"/>
-      <c r="I20" s="15"/>
+      <c r="A20" s="16"/>
+      <c r="B20" s="17"/>
+      <c r="C20" s="16"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="17"/>
+      <c r="F20" s="16"/>
+      <c r="G20" s="16"/>
+      <c r="H20" s="17"/>
+      <c r="I20" s="17"/>
     </row>
     <row r="21" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="14"/>
-      <c r="B21" s="15"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="15"/>
-      <c r="I21" s="15"/>
+      <c r="A21" s="16"/>
+      <c r="B21" s="17"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="16"/>
+      <c r="H21" s="17"/>
+      <c r="I21" s="17"/>
     </row>
     <row r="22" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="14"/>
-      <c r="B22" s="15"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="15"/>
-      <c r="I22" s="15"/>
+      <c r="A22" s="16"/>
+      <c r="B22" s="17"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="16"/>
+      <c r="H22" s="17"/>
+      <c r="I22" s="17"/>
     </row>
     <row r="23" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="14"/>
-      <c r="B23" s="15"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="15"/>
-      <c r="I23" s="15"/>
+      <c r="A23" s="16"/>
+      <c r="B23" s="17"/>
+      <c r="C23" s="16"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="16"/>
+      <c r="G23" s="16"/>
+      <c r="H23" s="17"/>
+      <c r="I23" s="17"/>
     </row>
     <row r="24" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="14"/>
-      <c r="B24" s="15"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="15"/>
-      <c r="I24" s="15"/>
+      <c r="A24" s="16"/>
+      <c r="B24" s="17"/>
+      <c r="C24" s="16"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="17"/>
+      <c r="F24" s="16"/>
+      <c r="G24" s="16"/>
+      <c r="H24" s="17"/>
+      <c r="I24" s="17"/>
     </row>
     <row r="25" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="14"/>
-      <c r="B25" s="15"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="15"/>
-      <c r="I25" s="15"/>
+      <c r="A25" s="16"/>
+      <c r="B25" s="17"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="16"/>
+      <c r="G25" s="16"/>
+      <c r="H25" s="17"/>
+      <c r="I25" s="17"/>
     </row>
     <row r="26" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="14"/>
-      <c r="B26" s="15"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="15"/>
-      <c r="I26" s="15"/>
+      <c r="A26" s="16"/>
+      <c r="B26" s="17"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="17"/>
+      <c r="F26" s="16"/>
+      <c r="G26" s="16"/>
+      <c r="H26" s="17"/>
+      <c r="I26" s="17"/>
     </row>
     <row r="27" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="14"/>
-      <c r="B27" s="15"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="15"/>
-      <c r="I27" s="15"/>
+      <c r="A27" s="16"/>
+      <c r="B27" s="17"/>
+      <c r="C27" s="16"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="16"/>
+      <c r="G27" s="16"/>
+      <c r="H27" s="17"/>
+      <c r="I27" s="17"/>
     </row>
     <row r="28" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="14"/>
-      <c r="B28" s="15"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="15"/>
-      <c r="I28" s="15"/>
+      <c r="A28" s="16"/>
+      <c r="B28" s="17"/>
+      <c r="C28" s="16"/>
+      <c r="D28" s="17"/>
+      <c r="E28" s="17"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="16"/>
+      <c r="H28" s="17"/>
+      <c r="I28" s="17"/>
     </row>
     <row r="29" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="14"/>
-      <c r="B29" s="15"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="15"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="15"/>
-      <c r="I29" s="15"/>
+      <c r="A29" s="16"/>
+      <c r="B29" s="17"/>
+      <c r="C29" s="16"/>
+      <c r="D29" s="17"/>
+      <c r="E29" s="17"/>
+      <c r="F29" s="16"/>
+      <c r="G29" s="16"/>
+      <c r="H29" s="17"/>
+      <c r="I29" s="17"/>
     </row>
     <row r="30" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="14"/>
-      <c r="B30" s="15"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="15"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="15"/>
-      <c r="I30" s="15"/>
+      <c r="A30" s="16"/>
+      <c r="B30" s="17"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="17"/>
+      <c r="E30" s="17"/>
+      <c r="F30" s="16"/>
+      <c r="G30" s="16"/>
+      <c r="H30" s="17"/>
+      <c r="I30" s="17"/>
     </row>
     <row r="31" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="14"/>
-      <c r="B31" s="15"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="15"/>
-      <c r="I31" s="15"/>
+      <c r="A31" s="16"/>
+      <c r="B31" s="17"/>
+      <c r="C31" s="16"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="17"/>
+      <c r="F31" s="16"/>
+      <c r="G31" s="16"/>
+      <c r="H31" s="17"/>
+      <c r="I31" s="17"/>
     </row>
     <row r="32" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="14"/>
-      <c r="B32" s="15"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="15"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="15"/>
-      <c r="I32" s="15"/>
+      <c r="A32" s="16"/>
+      <c r="B32" s="17"/>
+      <c r="C32" s="16"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="17"/>
+      <c r="F32" s="16"/>
+      <c r="G32" s="16"/>
+      <c r="H32" s="17"/>
+      <c r="I32" s="17"/>
     </row>
     <row r="33" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="14"/>
-      <c r="B33" s="15"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="15"/>
-      <c r="E33" s="15"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="15"/>
-      <c r="I33" s="15"/>
+      <c r="A33" s="16"/>
+      <c r="B33" s="17"/>
+      <c r="C33" s="16"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="17"/>
+      <c r="F33" s="16"/>
+      <c r="G33" s="16"/>
+      <c r="H33" s="17"/>
+      <c r="I33" s="17"/>
     </row>
     <row r="34" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="14"/>
-      <c r="B34" s="15"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="15"/>
-      <c r="E34" s="15"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="15"/>
-      <c r="I34" s="15"/>
+      <c r="A34" s="16"/>
+      <c r="B34" s="17"/>
+      <c r="C34" s="16"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="17"/>
+      <c r="F34" s="16"/>
+      <c r="G34" s="16"/>
+      <c r="H34" s="17"/>
+      <c r="I34" s="17"/>
     </row>
     <row r="35" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="14"/>
-      <c r="B35" s="15"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="15"/>
-      <c r="E35" s="15"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="15"/>
-      <c r="I35" s="15"/>
+      <c r="A35" s="16"/>
+      <c r="B35" s="17"/>
+      <c r="C35" s="16"/>
+      <c r="D35" s="17"/>
+      <c r="E35" s="17"/>
+      <c r="F35" s="16"/>
+      <c r="G35" s="16"/>
+      <c r="H35" s="17"/>
+      <c r="I35" s="17"/>
     </row>
     <row r="36" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="14"/>
-      <c r="B36" s="15"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="15"/>
-      <c r="E36" s="15"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="15"/>
-      <c r="I36" s="15"/>
+      <c r="A36" s="16"/>
+      <c r="B36" s="17"/>
+      <c r="C36" s="16"/>
+      <c r="D36" s="17"/>
+      <c r="E36" s="17"/>
+      <c r="F36" s="16"/>
+      <c r="G36" s="16"/>
+      <c r="H36" s="17"/>
+      <c r="I36" s="17"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2905,12 +3673,12 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I36"/>
-  <sheetFormatPr defaultColWidth="11.0234375" defaultRowHeight="17.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.02734375" defaultRowHeight="17.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="15.63"/>
@@ -2925,468 +3693,468 @@
   </cols>
   <sheetData>
     <row r="1" s="4" customFormat="true" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="15" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="E2" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="17"/>
+    </row>
+    <row r="4" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="B4" s="17"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="E4" s="17"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
+    </row>
+    <row r="5" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="B5" s="17"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="E5" s="17"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="17"/>
+      <c r="I5" s="17"/>
+    </row>
+    <row r="6" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="16"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="E6" s="17"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
+    </row>
+    <row r="7" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="16"/>
+      <c r="B7" s="17"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="E7" s="17"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="17"/>
+      <c r="I7" s="17"/>
+    </row>
+    <row r="8" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="16"/>
+      <c r="B8" s="17"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="E8" s="17"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="17"/>
+    </row>
+    <row r="9" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="16"/>
+      <c r="B9" s="17"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="E9" s="17"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="17" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="16"/>
+      <c r="B10" s="17"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="E10" s="17"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="H10" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="B2" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="C2" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="D2" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="E2" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="14" t="s">
-        <v>111</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>112</v>
-      </c>
-      <c r="C3" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
-      <c r="H3" s="15"/>
-      <c r="I3" s="15"/>
-    </row>
-    <row r="4" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="14" t="s">
-        <v>114</v>
-      </c>
-      <c r="B4" s="15"/>
-      <c r="C4" s="14"/>
-      <c r="D4" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="E4" s="15"/>
-      <c r="F4" s="14"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="15"/>
-      <c r="I4" s="15"/>
-    </row>
-    <row r="5" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="B5" s="15"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="E5" s="15"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14"/>
-      <c r="H5" s="15"/>
-      <c r="I5" s="15"/>
-    </row>
-    <row r="6" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="14"/>
-      <c r="B6" s="15"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="E6" s="15"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14"/>
-      <c r="H6" s="15"/>
-      <c r="I6" s="15"/>
-    </row>
-    <row r="7" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="14"/>
-      <c r="B7" s="15"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="E7" s="15"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="15"/>
-      <c r="I7" s="15"/>
-    </row>
-    <row r="8" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="14"/>
-      <c r="B8" s="15"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="E8" s="15"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="15"/>
-    </row>
-    <row r="9" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="14"/>
-      <c r="B9" s="15"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="E9" s="15"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="15" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="14"/>
-      <c r="B10" s="15"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="E10" s="15"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="H10" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="I10" s="15" t="s">
+      <c r="I10" s="17" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="14"/>
-      <c r="B11" s="15"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="15"/>
-      <c r="I11" s="15"/>
+      <c r="A11" s="16"/>
+      <c r="B11" s="17"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="17"/>
+      <c r="I11" s="17"/>
     </row>
     <row r="12" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="14"/>
-      <c r="B12" s="15"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="15"/>
-      <c r="I12" s="15"/>
+      <c r="A12" s="16"/>
+      <c r="B12" s="17"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="17"/>
     </row>
     <row r="13" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="14"/>
-      <c r="B13" s="15"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="15"/>
-      <c r="I13" s="15"/>
+      <c r="A13" s="16"/>
+      <c r="B13" s="17"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="17"/>
+      <c r="I13" s="17"/>
     </row>
     <row r="14" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="14"/>
-      <c r="B14" s="15"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="15"/>
-      <c r="I14" s="15"/>
+      <c r="A14" s="16"/>
+      <c r="B14" s="17"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="17"/>
+      <c r="I14" s="17"/>
     </row>
     <row r="15" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="14"/>
-      <c r="B15" s="15"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="15"/>
-      <c r="I15" s="15"/>
+      <c r="A15" s="16"/>
+      <c r="B15" s="17"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="17"/>
+      <c r="I15" s="17"/>
     </row>
     <row r="16" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="14"/>
-      <c r="B16" s="15"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="15"/>
-      <c r="I16" s="15"/>
+      <c r="A16" s="16"/>
+      <c r="B16" s="17"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="17"/>
+      <c r="I16" s="17"/>
     </row>
     <row r="17" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="14"/>
-      <c r="B17" s="15"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="15"/>
-      <c r="I17" s="15"/>
+      <c r="A17" s="16"/>
+      <c r="B17" s="17"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="17"/>
+      <c r="I17" s="17"/>
     </row>
     <row r="18" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="14"/>
-      <c r="B18" s="15"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="15"/>
-      <c r="I18" s="15"/>
+      <c r="A18" s="16"/>
+      <c r="B18" s="17"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="16"/>
+      <c r="H18" s="17"/>
+      <c r="I18" s="17"/>
     </row>
     <row r="19" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="14"/>
-      <c r="B19" s="15"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="15"/>
-      <c r="I19" s="15"/>
+      <c r="A19" s="16"/>
+      <c r="B19" s="17"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="16"/>
+      <c r="H19" s="17"/>
+      <c r="I19" s="17"/>
     </row>
     <row r="20" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="14"/>
-      <c r="B20" s="15"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="15"/>
-      <c r="I20" s="15"/>
+      <c r="A20" s="16"/>
+      <c r="B20" s="17"/>
+      <c r="C20" s="16"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="17"/>
+      <c r="F20" s="16"/>
+      <c r="G20" s="16"/>
+      <c r="H20" s="17"/>
+      <c r="I20" s="17"/>
     </row>
     <row r="21" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="14"/>
-      <c r="B21" s="15"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="15"/>
-      <c r="I21" s="15"/>
+      <c r="A21" s="16"/>
+      <c r="B21" s="17"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="16"/>
+      <c r="H21" s="17"/>
+      <c r="I21" s="17"/>
     </row>
     <row r="22" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="14"/>
-      <c r="B22" s="15"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="15"/>
-      <c r="I22" s="15"/>
+      <c r="A22" s="16"/>
+      <c r="B22" s="17"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="16"/>
+      <c r="H22" s="17"/>
+      <c r="I22" s="17"/>
     </row>
     <row r="23" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="14"/>
-      <c r="B23" s="15"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="15"/>
-      <c r="I23" s="15"/>
+      <c r="A23" s="16"/>
+      <c r="B23" s="17"/>
+      <c r="C23" s="16"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="16"/>
+      <c r="G23" s="16"/>
+      <c r="H23" s="17"/>
+      <c r="I23" s="17"/>
     </row>
     <row r="24" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="14"/>
-      <c r="B24" s="15"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="15"/>
-      <c r="I24" s="15"/>
+      <c r="A24" s="16"/>
+      <c r="B24" s="17"/>
+      <c r="C24" s="16"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="17"/>
+      <c r="F24" s="16"/>
+      <c r="G24" s="16"/>
+      <c r="H24" s="17"/>
+      <c r="I24" s="17"/>
     </row>
     <row r="25" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="14"/>
-      <c r="B25" s="15"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="15"/>
-      <c r="I25" s="15"/>
+      <c r="A25" s="16"/>
+      <c r="B25" s="17"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="16"/>
+      <c r="G25" s="16"/>
+      <c r="H25" s="17"/>
+      <c r="I25" s="17"/>
     </row>
     <row r="26" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="14"/>
-      <c r="B26" s="15"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="15"/>
-      <c r="I26" s="15"/>
+      <c r="A26" s="16"/>
+      <c r="B26" s="17"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="17"/>
+      <c r="F26" s="16"/>
+      <c r="G26" s="16"/>
+      <c r="H26" s="17"/>
+      <c r="I26" s="17"/>
     </row>
     <row r="27" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="14"/>
-      <c r="B27" s="15"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="15"/>
-      <c r="I27" s="15"/>
+      <c r="A27" s="16"/>
+      <c r="B27" s="17"/>
+      <c r="C27" s="16"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="16"/>
+      <c r="G27" s="16"/>
+      <c r="H27" s="17"/>
+      <c r="I27" s="17"/>
     </row>
     <row r="28" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="14"/>
-      <c r="B28" s="15"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="15"/>
-      <c r="I28" s="15"/>
+      <c r="A28" s="16"/>
+      <c r="B28" s="17"/>
+      <c r="C28" s="16"/>
+      <c r="D28" s="17"/>
+      <c r="E28" s="17"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="16"/>
+      <c r="H28" s="17"/>
+      <c r="I28" s="17"/>
     </row>
     <row r="29" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="14"/>
-      <c r="B29" s="15"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="15"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="15"/>
-      <c r="I29" s="15"/>
+      <c r="A29" s="16"/>
+      <c r="B29" s="17"/>
+      <c r="C29" s="16"/>
+      <c r="D29" s="17"/>
+      <c r="E29" s="17"/>
+      <c r="F29" s="16"/>
+      <c r="G29" s="16"/>
+      <c r="H29" s="17"/>
+      <c r="I29" s="17"/>
     </row>
     <row r="30" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="14"/>
-      <c r="B30" s="15"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="15"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="15"/>
-      <c r="I30" s="15"/>
+      <c r="A30" s="16"/>
+      <c r="B30" s="17"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="17"/>
+      <c r="E30" s="17"/>
+      <c r="F30" s="16"/>
+      <c r="G30" s="16"/>
+      <c r="H30" s="17"/>
+      <c r="I30" s="17"/>
     </row>
     <row r="31" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="14"/>
-      <c r="B31" s="15"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="15"/>
-      <c r="I31" s="15"/>
+      <c r="A31" s="16"/>
+      <c r="B31" s="17"/>
+      <c r="C31" s="16"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="17"/>
+      <c r="F31" s="16"/>
+      <c r="G31" s="16"/>
+      <c r="H31" s="17"/>
+      <c r="I31" s="17"/>
     </row>
     <row r="32" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="14"/>
-      <c r="B32" s="15"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="15"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="15"/>
-      <c r="I32" s="15"/>
+      <c r="A32" s="16"/>
+      <c r="B32" s="17"/>
+      <c r="C32" s="16"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="17"/>
+      <c r="F32" s="16"/>
+      <c r="G32" s="16"/>
+      <c r="H32" s="17"/>
+      <c r="I32" s="17"/>
     </row>
     <row r="33" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="14"/>
-      <c r="B33" s="15"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="15"/>
-      <c r="E33" s="15"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="15"/>
-      <c r="I33" s="15"/>
+      <c r="A33" s="16"/>
+      <c r="B33" s="17"/>
+      <c r="C33" s="16"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="17"/>
+      <c r="F33" s="16"/>
+      <c r="G33" s="16"/>
+      <c r="H33" s="17"/>
+      <c r="I33" s="17"/>
     </row>
     <row r="34" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="14"/>
-      <c r="B34" s="15"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="15"/>
-      <c r="E34" s="15"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="15"/>
-      <c r="I34" s="15"/>
+      <c r="A34" s="16"/>
+      <c r="B34" s="17"/>
+      <c r="C34" s="16"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="17"/>
+      <c r="F34" s="16"/>
+      <c r="G34" s="16"/>
+      <c r="H34" s="17"/>
+      <c r="I34" s="17"/>
     </row>
     <row r="35" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="14"/>
-      <c r="B35" s="15"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="15"/>
-      <c r="E35" s="15"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="15"/>
-      <c r="I35" s="15"/>
+      <c r="A35" s="16"/>
+      <c r="B35" s="17"/>
+      <c r="C35" s="16"/>
+      <c r="D35" s="17"/>
+      <c r="E35" s="17"/>
+      <c r="F35" s="16"/>
+      <c r="G35" s="16"/>
+      <c r="H35" s="17"/>
+      <c r="I35" s="17"/>
     </row>
     <row r="36" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="14"/>
-      <c r="B36" s="15"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="15"/>
-      <c r="E36" s="15"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="15"/>
-      <c r="I36" s="15"/>
+      <c r="A36" s="16"/>
+      <c r="B36" s="17"/>
+      <c r="C36" s="16"/>
+      <c r="D36" s="17"/>
+      <c r="E36" s="17"/>
+      <c r="F36" s="16"/>
+      <c r="G36" s="16"/>
+      <c r="H36" s="17"/>
+      <c r="I36" s="17"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -3400,12 +4168,12 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.91796875" defaultRowHeight="17.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.91796875" defaultRowHeight="17.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
